--- a/RM.xlsx
+++ b/RM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F18E441-2861-46F4-8BF8-98D72D4AA6C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7095FE51-91DA-4C79-AB03-677CED8E7133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4956" uniqueCount="2566">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4998" uniqueCount="2587">
   <si>
     <t>ID</t>
   </si>
@@ -8269,6 +8269,84 @@
   </si>
   <si>
     <t>SCJ Nice TR PURPLE ONION 8115334610 PET</t>
+  </si>
+  <si>
+    <t>RM246.2</t>
+  </si>
+  <si>
+    <t>Pet Preform 83mm 45gm ROPP Clear SBPP</t>
+  </si>
+  <si>
+    <t>PET Preform 45gm 83mm</t>
+  </si>
+  <si>
+    <t>J.S-
+Wall Thickness: 1.76 mm to 2.82 mm
+W: 44.72gm to  45.18gm
+H: 84.32 mm
+CRH: 17.00 mm
+ID: 76.85 mm
+OD w/ thread: 82.35 mm
+OD w/o thread: 79.60 mm
+OD Head: 80.50 mm
+OD Neck Ring (Neck Size): 82.80 mm</t>
+  </si>
+  <si>
+    <t>RM087.7</t>
+  </si>
+  <si>
+    <t>Screw 53mm Plain Yellow Cap LP H=14.00, OD=54.50, W=4.20</t>
+  </si>
+  <si>
+    <t>53MM YELLOW SCREW CAPS</t>
+  </si>
+  <si>
+    <t>RM225.2</t>
+  </si>
+  <si>
+    <t>Screw 63mm Pearl Blue Cap UC</t>
+  </si>
+  <si>
+    <t>63mm Jar Cap Pearl Blue</t>
+  </si>
+  <si>
+    <t>Codification done prior Procurement on 31.07.2026</t>
+  </si>
+  <si>
+    <t>RM274</t>
+  </si>
+  <si>
+    <t>SCREW 100mm H=18.00, OD=104.00, W=14.00</t>
+  </si>
+  <si>
+    <t>RM274.1</t>
+  </si>
+  <si>
+    <t>Screw 100mm Red Cap UC</t>
+  </si>
+  <si>
+    <t>100mm Jar Cap Red</t>
+  </si>
+  <si>
+    <t>Codification based on Samples:
+Height: 17.87 mm
+Weight: 13.75 gm - 14.06 gm
+ID w/o thread: 101.50 mm
+ID thread: 98.50 mm - 98.98 mm
+O.D: 104.05 mm
+Wall Thickness: 1.03 mm</t>
+  </si>
+  <si>
+    <t>RM001.12</t>
+  </si>
+  <si>
+    <t>Pet Resin SUPET 320D GP-1150KG</t>
+  </si>
+  <si>
+    <t>Bottle Grade PET Chips  SUPET 320D GP 1150Kg</t>
+  </si>
+  <si>
+    <t>Procured from Singla Polysource.</t>
   </si>
 </sst>
 </file>
@@ -8452,7 +8530,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8797,20 +8877,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A19D9272-74F0-4140-89F8-AC25124E915C}" name="Table1" displayName="Table1" ref="A1:K559" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
-  <autoFilter ref="A1:K559" xr:uid="{A19D9272-74F0-4140-89F8-AC25124E915C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5EEF2ADA-3472-43C5-92EC-70F26BD235C4}" name="Table1" displayName="Table1" ref="A1:K564" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
+  <autoFilter ref="A1:K564" xr:uid="{5EEF2ADA-3472-43C5-92EC-70F26BD235C4}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{ED2EF6EF-0EB7-4112-A26A-587360A50162}" name="ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{FD04631D-D00C-4A85-A2D3-B270D1FE8686}" name="Status" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{452A9C79-F513-4556-9DAA-C4E72A9C9794}" name="Material List::Material_Detail" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{637A1E06-74A7-490F-894F-219A47C183BB}" name="Product_Code" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{2FDB4226-7F15-4C2D-AE55-0449A0BC4802}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{B8ECC17F-1531-4404-AFF9-6FD59393FC5C}" name="Item_Code" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{9CDAF27F-B4A2-41DB-B042-54F5483B4C54}" name="Old_Item_Code" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{679FFD2C-0F99-451A-8946-09878C496DEF}" name="Item_Name" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{C363CCC7-2B54-4B87-BB4F-4D4263978256}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{16FC478C-37F1-4094-84A3-E55D974BDC77}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{50C50C0E-3494-45F7-A277-BBBEEB8D1D70}" name="Remarks" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{2B76E7E7-6B68-4D47-BFF1-E615A0FA607F}" name="ID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{840B42E3-6C72-48D2-9D61-805D6681F1D8}" name="Status" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{0D107CD3-EE23-4C93-9E8D-8BEB612E0B3C}" name="Material List::Material_Detail" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{6298C241-A153-4A68-8A1F-A9D9E6DE38B5}" name="Product_Code" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{E6725181-5FD0-4222-8F0A-B2992203A3F0}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{7869C7FD-3885-4438-B56D-7710FBECA340}" name="Item_Code" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{D3383CFD-D70B-4F19-8A4F-56E3F4C815BD}" name="Old_Item_Code" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{62A15C81-E445-4797-999A-8A3E09ECCDFA}" name="Item_Name" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{442F045B-3DDC-4C0C-9C56-A2D378E41E09}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{6E26E371-86C4-4387-925D-CCFC09D0B3F6}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{CAE80267-2610-42DB-BD00-4E36B662DD5D}" name="Remarks" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9113,7 +9193,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K559"/>
+  <dimension ref="A1:K564"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -27394,38 +27474,197 @@
       </c>
     </row>
     <row r="559" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A559" s="9">
+      <c r="A559" s="4">
         <v>559</v>
       </c>
-      <c r="B559" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C559" s="10" t="s">
+      <c r="B559" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C559" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D559" s="10" t="s">
+      <c r="D559" s="5" t="s">
         <v>2562</v>
       </c>
-      <c r="E559" s="10" t="s">
+      <c r="E559" s="5" t="s">
         <v>2563</v>
       </c>
-      <c r="F559" s="10" t="s">
+      <c r="F559" s="5" t="s">
         <v>2564</v>
       </c>
-      <c r="G559" s="11"/>
-      <c r="H559" s="10" t="s">
+      <c r="G559" s="7"/>
+      <c r="H559" s="5" t="s">
         <v>2565</v>
       </c>
-      <c r="I559" s="10" t="s">
+      <c r="I559" s="5" t="s">
         <v>2536</v>
       </c>
-      <c r="J559" s="10" t="s">
+      <c r="J559" s="5" t="s">
         <v>2529</v>
       </c>
-      <c r="K559" s="12"/>
+      <c r="K559" s="6"/>
+    </row>
+    <row r="560" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A560" s="4">
+        <v>560</v>
+      </c>
+      <c r="B560" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C560" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="D560" s="5" t="s">
+        <v>2270</v>
+      </c>
+      <c r="E560" s="5" t="s">
+        <v>2271</v>
+      </c>
+      <c r="F560" s="5" t="s">
+        <v>2566</v>
+      </c>
+      <c r="G560" s="7"/>
+      <c r="H560" s="5" t="s">
+        <v>2567</v>
+      </c>
+      <c r="I560" s="5" t="s">
+        <v>2568</v>
+      </c>
+      <c r="J560" s="5" t="s">
+        <v>619</v>
+      </c>
+      <c r="K560" s="8" t="s">
+        <v>2569</v>
+      </c>
+    </row>
+    <row r="561" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A561" s="4">
+        <v>561</v>
+      </c>
+      <c r="B561" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C561" s="5" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D561" s="5" t="s">
+        <v>1575</v>
+      </c>
+      <c r="E561" s="5" t="s">
+        <v>1576</v>
+      </c>
+      <c r="F561" s="5" t="s">
+        <v>2570</v>
+      </c>
+      <c r="G561" s="7"/>
+      <c r="H561" s="5" t="s">
+        <v>2571</v>
+      </c>
+      <c r="I561" s="5" t="s">
+        <v>2572</v>
+      </c>
+      <c r="J561" s="5" t="s">
+        <v>1524</v>
+      </c>
+      <c r="K561" s="6"/>
+    </row>
+    <row r="562" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A562" s="4">
+        <v>562</v>
+      </c>
+      <c r="B562" s="7"/>
+      <c r="C562" s="5" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D562" s="5" t="s">
+        <v>2040</v>
+      </c>
+      <c r="E562" s="5" t="s">
+        <v>2041</v>
+      </c>
+      <c r="F562" s="5" t="s">
+        <v>2573</v>
+      </c>
+      <c r="G562" s="7"/>
+      <c r="H562" s="5" t="s">
+        <v>2574</v>
+      </c>
+      <c r="I562" s="5" t="s">
+        <v>2575</v>
+      </c>
+      <c r="J562" s="5" t="s">
+        <v>1479</v>
+      </c>
+      <c r="K562" s="8" t="s">
+        <v>2576</v>
+      </c>
+    </row>
+    <row r="563" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A563" s="4">
+        <v>563</v>
+      </c>
+      <c r="B563" s="7"/>
+      <c r="C563" s="5" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D563" s="5" t="s">
+        <v>2577</v>
+      </c>
+      <c r="E563" s="5" t="s">
+        <v>2578</v>
+      </c>
+      <c r="F563" s="5" t="s">
+        <v>2579</v>
+      </c>
+      <c r="G563" s="7"/>
+      <c r="H563" s="5" t="s">
+        <v>2580</v>
+      </c>
+      <c r="I563" s="5" t="s">
+        <v>2581</v>
+      </c>
+      <c r="J563" s="5" t="s">
+        <v>1479</v>
+      </c>
+      <c r="K563" s="8" t="s">
+        <v>2582</v>
+      </c>
+    </row>
+    <row r="564" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A564" s="9">
+        <v>564</v>
+      </c>
+      <c r="B564" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C564" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D564" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E564" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F564" s="10" t="s">
+        <v>2583</v>
+      </c>
+      <c r="G564" s="11"/>
+      <c r="H564" s="10" t="s">
+        <v>2584</v>
+      </c>
+      <c r="I564" s="10" t="s">
+        <v>2585</v>
+      </c>
+      <c r="J564" s="10" t="s">
+        <v>555</v>
+      </c>
+      <c r="K564" s="12" t="s">
+        <v>2586</v>
+      </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="blHOPAnLpH79WayCqSNB8zHEmfilVFGj/xCf2DUXiv7v6Clu9L52Kw8Shj0lPNws73ZHJTmM/wxWow5TGTGfxA==" saltValue="vjLWhPuhq7o4w8gXCJVt1w==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Jm63/Aplr1ieozR90tRu+Dwh7BVcwoJT2J3ikOa/9LtZ7EbYBJEDhXYlGHPLd4FHMBd/drhamfhwkuES6J+9pg==" saltValue="Ectll0vsHTXmjgjYZvQzCw==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/RM.xlsx
+++ b/RM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7095FE51-91DA-4C79-AB03-677CED8E7133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B748F0AE-847A-424A-B971-D7F0DC729B78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4998" uniqueCount="2587">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5007" uniqueCount="2593">
   <si>
     <t>ID</t>
   </si>
@@ -8347,6 +8347,27 @@
   </si>
   <si>
     <t>Procured from Singla Polysource.</t>
+  </si>
+  <si>
+    <t>RM275</t>
+  </si>
+  <si>
+    <t>INNER PLUG 25mm B Drop H=21.70 , OD=22.10 , W=1.00</t>
+  </si>
+  <si>
+    <t>RM275.1</t>
+  </si>
+  <si>
+    <t>25mm Inner Plug B Drop Natural LP</t>
+  </si>
+  <si>
+    <t>PLASTIC B. DROP NO. 10 LOCK</t>
+  </si>
+  <si>
+    <t>Height (with Nozzle): 21.70 mm
+Height (without Nozzle): 10.00 mm
+OD: 22.10 mm
+Weight: 1.00 gm</t>
   </si>
 </sst>
 </file>
@@ -8538,41 +8559,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="16">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -8838,13 +8824,6 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -8863,6 +8842,48 @@
     <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -8877,20 +8898,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5EEF2ADA-3472-43C5-92EC-70F26BD235C4}" name="Table1" displayName="Table1" ref="A1:K564" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
-  <autoFilter ref="A1:K564" xr:uid="{5EEF2ADA-3472-43C5-92EC-70F26BD235C4}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A9EB3DCE-D3FD-42E8-A004-943CFC3E6A4C}" name="Table1" displayName="Table1" ref="A1:K565" totalsRowShown="0" headerRowDxfId="15" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12" totalsRowBorderDxfId="11">
+  <autoFilter ref="A1:K565" xr:uid="{A9EB3DCE-D3FD-42E8-A004-943CFC3E6A4C}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{2B76E7E7-6B68-4D47-BFF1-E615A0FA607F}" name="ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{840B42E3-6C72-48D2-9D61-805D6681F1D8}" name="Status" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{0D107CD3-EE23-4C93-9E8D-8BEB612E0B3C}" name="Material List::Material_Detail" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{6298C241-A153-4A68-8A1F-A9D9E6DE38B5}" name="Product_Code" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{E6725181-5FD0-4222-8F0A-B2992203A3F0}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{7869C7FD-3885-4438-B56D-7710FBECA340}" name="Item_Code" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{D3383CFD-D70B-4F19-8A4F-56E3F4C815BD}" name="Old_Item_Code" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{62A15C81-E445-4797-999A-8A3E09ECCDFA}" name="Item_Name" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{442F045B-3DDC-4C0C-9C56-A2D378E41E09}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{6E26E371-86C4-4387-925D-CCFC09D0B3F6}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{CAE80267-2610-42DB-BD00-4E36B662DD5D}" name="Remarks" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{E3FE84C3-713C-4160-B75A-A921A02BEAC2}" name="ID" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{E11320B3-0215-4D1F-BC01-CF0070D0BE6B}" name="Status" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{E0CE7ECF-F143-4B01-9318-F75A8D0C55E1}" name="Material List::Material_Detail" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{34972B56-78AD-4773-9941-3034D1FDEAD5}" name="Product_Code" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{E912AEE3-DBB6-48D4-B421-A1CB783AC5FF}" name="RM PM Product List 2::Product_Detail" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{0668274F-F887-4D31-82A0-D7133C6B1899}" name="Item_Code" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{CE92684E-8805-46C3-9D9D-147D4F4C5E0B}" name="Old_Item_Code" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{27C4125C-F511-4663-A161-086C0D5F90EE}" name="Item_Name" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{88ABFC3B-7C45-48F7-BFE1-1644F876A8C7}" name="Item_Detail_by_Vendor" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{216BDBB2-1E1B-4234-BA1F-63A93F5FE749}" name="Vendor List 2::Vendor_Name" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{6DAD74E1-AFF6-41B9-9433-F065B6C8BEAB}" name="Remarks" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9193,7 +9214,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K564"/>
+  <dimension ref="A1:K565"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -27631,40 +27652,73 @@
       </c>
     </row>
     <row r="564" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A564" s="9">
+      <c r="A564" s="4">
         <v>564</v>
       </c>
-      <c r="B564" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C564" s="10" t="s">
+      <c r="B564" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C564" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D564" s="10" t="s">
+      <c r="D564" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E564" s="10" t="s">
+      <c r="E564" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F564" s="10" t="s">
+      <c r="F564" s="5" t="s">
         <v>2583</v>
       </c>
-      <c r="G564" s="11"/>
-      <c r="H564" s="10" t="s">
+      <c r="G564" s="7"/>
+      <c r="H564" s="5" t="s">
         <v>2584</v>
       </c>
-      <c r="I564" s="10" t="s">
+      <c r="I564" s="5" t="s">
         <v>2585</v>
       </c>
-      <c r="J564" s="10" t="s">
+      <c r="J564" s="5" t="s">
         <v>555</v>
       </c>
-      <c r="K564" s="12" t="s">
+      <c r="K564" s="8" t="s">
         <v>2586</v>
       </c>
     </row>
+    <row r="565" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A565" s="9">
+        <v>565</v>
+      </c>
+      <c r="B565" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C565" s="10" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D565" s="10" t="s">
+        <v>2587</v>
+      </c>
+      <c r="E565" s="10" t="s">
+        <v>2588</v>
+      </c>
+      <c r="F565" s="10" t="s">
+        <v>2589</v>
+      </c>
+      <c r="G565" s="11"/>
+      <c r="H565" s="10" t="s">
+        <v>2590</v>
+      </c>
+      <c r="I565" s="10" t="s">
+        <v>2591</v>
+      </c>
+      <c r="J565" s="10" t="s">
+        <v>1524</v>
+      </c>
+      <c r="K565" s="12" t="s">
+        <v>2592</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Jm63/Aplr1ieozR90tRu+Dwh7BVcwoJT2J3ikOa/9LtZ7EbYBJEDhXYlGHPLd4FHMBd/drhamfhwkuES6J+9pg==" saltValue="Ectll0vsHTXmjgjYZvQzCw==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Al6SqGmj30Y5vw7N3pn08WeZLrQq+LZBhWmK+Z3G5mQSnqmVWeRon9I56bNrnVz/ONsVg8umQqKuLWx6lv9sXw==" saltValue="PCs6bvrwR9LdBd1AfkJlqg==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/RM.xlsx
+++ b/RM.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KANU\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B748F0AE-847A-424A-B971-D7F0DC729B78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8235"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5007" uniqueCount="2593">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5023" uniqueCount="2600">
   <si>
     <t>ID</t>
   </si>
@@ -8369,11 +8368,32 @@
 OD: 22.10 mm
 Weight: 1.00 gm</t>
   </si>
+  <si>
+    <t>RM087.8</t>
+  </si>
+  <si>
+    <t>Screw 53mm Black Short Cap</t>
+  </si>
+  <si>
+    <t>ULTRA 53MM JAR CAP (BLACK)</t>
+  </si>
+  <si>
+    <t>TO BE PROCURED........</t>
+  </si>
+  <si>
+    <t>RM002.18</t>
+  </si>
+  <si>
+    <t>Pet Resin FLEX PET TM -1200Kgs</t>
+  </si>
+  <si>
+    <t>Product: CP-BG-CHIPS-XX-B; Grade: Flex-PET TM</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -8524,42 +8544,90 @@
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="16">
     <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -8582,6 +8650,21 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -8606,6 +8689,21 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -8630,6 +8728,21 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -8676,6 +8789,21 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -8700,6 +8828,21 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -8724,6 +8867,21 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -8748,6 +8906,21 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -8772,6 +8945,21 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -8796,6 +8984,22 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
@@ -8824,6 +9028,13 @@
       </border>
     </dxf>
     <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -8840,18 +9051,8 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <font>
-        <b/>
+        <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -8863,26 +9064,9 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Calibri"/>
-        <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -8898,20 +9082,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A9EB3DCE-D3FD-42E8-A004-943CFC3E6A4C}" name="Table1" displayName="Table1" ref="A1:K565" totalsRowShown="0" headerRowDxfId="15" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12" totalsRowBorderDxfId="11">
-  <autoFilter ref="A1:K565" xr:uid="{A9EB3DCE-D3FD-42E8-A004-943CFC3E6A4C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:K567" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
+  <autoFilter ref="A1:K567"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{E3FE84C3-713C-4160-B75A-A921A02BEAC2}" name="ID" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{E11320B3-0215-4D1F-BC01-CF0070D0BE6B}" name="Status" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{E0CE7ECF-F143-4B01-9318-F75A8D0C55E1}" name="Material List::Material_Detail" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{34972B56-78AD-4773-9941-3034D1FDEAD5}" name="Product_Code" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{E912AEE3-DBB6-48D4-B421-A1CB783AC5FF}" name="RM PM Product List 2::Product_Detail" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{0668274F-F887-4D31-82A0-D7133C6B1899}" name="Item_Code" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{CE92684E-8805-46C3-9D9D-147D4F4C5E0B}" name="Old_Item_Code" dataDxfId="4"/>
-    <tableColumn id="8" xr3:uid="{27C4125C-F511-4663-A161-086C0D5F90EE}" name="Item_Name" dataDxfId="3"/>
-    <tableColumn id="9" xr3:uid="{88ABFC3B-7C45-48F7-BFE1-1644F876A8C7}" name="Item_Detail_by_Vendor" dataDxfId="2"/>
-    <tableColumn id="10" xr3:uid="{216BDBB2-1E1B-4234-BA1F-63A93F5FE749}" name="Vendor List 2::Vendor_Name" dataDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{6DAD74E1-AFF6-41B9-9433-F065B6C8BEAB}" name="Remarks" dataDxfId="0"/>
+    <tableColumn id="1" name="ID" dataDxfId="11"/>
+    <tableColumn id="2" name="Status" dataDxfId="10"/>
+    <tableColumn id="3" name="Material List::Material_Detail" dataDxfId="9"/>
+    <tableColumn id="4" name="Product_Code" dataDxfId="8"/>
+    <tableColumn id="5" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
+    <tableColumn id="6" name="Item_Code" dataDxfId="6"/>
+    <tableColumn id="7" name="Old_Item_Code" dataDxfId="5"/>
+    <tableColumn id="8" name="Item_Name" dataDxfId="4"/>
+    <tableColumn id="9" name="Item_Detail_by_Vendor" dataDxfId="3"/>
+    <tableColumn id="10" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
+    <tableColumn id="11" name="Remarks" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8934,7 +9118,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -8946,7 +9130,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -8963,9 +9147,9 @@
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -8993,31 +9177,14 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -9045,23 +9212,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -9213,8 +9363,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K565"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K567"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -27685,40 +27835,102 @@
       </c>
     </row>
     <row r="565" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A565" s="9">
+      <c r="A565" s="4">
         <v>565</v>
       </c>
-      <c r="B565" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C565" s="10" t="s">
+      <c r="B565" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C565" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="D565" s="10" t="s">
+      <c r="D565" s="5" t="s">
         <v>2587</v>
       </c>
-      <c r="E565" s="10" t="s">
+      <c r="E565" s="5" t="s">
         <v>2588</v>
       </c>
-      <c r="F565" s="10" t="s">
+      <c r="F565" s="5" t="s">
         <v>2589</v>
       </c>
-      <c r="G565" s="11"/>
-      <c r="H565" s="10" t="s">
+      <c r="G565" s="7"/>
+      <c r="H565" s="5" t="s">
         <v>2590</v>
       </c>
-      <c r="I565" s="10" t="s">
+      <c r="I565" s="5" t="s">
         <v>2591</v>
       </c>
-      <c r="J565" s="10" t="s">
+      <c r="J565" s="5" t="s">
         <v>1524</v>
       </c>
-      <c r="K565" s="12" t="s">
+      <c r="K565" s="8" t="s">
         <v>2592</v>
       </c>
     </row>
+    <row r="566" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A566" s="4">
+        <v>566</v>
+      </c>
+      <c r="B566" s="7"/>
+      <c r="C566" s="5" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D566" s="5" t="s">
+        <v>1575</v>
+      </c>
+      <c r="E566" s="5" t="s">
+        <v>1576</v>
+      </c>
+      <c r="F566" s="5" t="s">
+        <v>2593</v>
+      </c>
+      <c r="G566" s="7"/>
+      <c r="H566" s="5" t="s">
+        <v>2594</v>
+      </c>
+      <c r="I566" s="5" t="s">
+        <v>2595</v>
+      </c>
+      <c r="J566" s="5" t="s">
+        <v>1479</v>
+      </c>
+      <c r="K566" s="8" t="s">
+        <v>2596</v>
+      </c>
+    </row>
+    <row r="567" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A567" s="9">
+        <v>567</v>
+      </c>
+      <c r="B567" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C567" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D567" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E567" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F567" s="10" t="s">
+        <v>2597</v>
+      </c>
+      <c r="G567" s="11"/>
+      <c r="H567" s="10" t="s">
+        <v>2598</v>
+      </c>
+      <c r="I567" s="10" t="s">
+        <v>2599</v>
+      </c>
+      <c r="J567" s="10" t="s">
+        <v>2171</v>
+      </c>
+      <c r="K567" s="12"/>
+    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Al6SqGmj30Y5vw7N3pn08WeZLrQq+LZBhWmK+Z3G5mQSnqmVWeRon9I56bNrnVz/ONsVg8umQqKuLWx6lv9sXw==" saltValue="PCs6bvrwR9LdBd1AfkJlqg==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="/gdxXmsyrUy0Xgpr/aQXcP9UR6tHGKp4EZH1tUgRDZ25wnJNXa0FrZsrRWuruiCYpnzzNrbLrMl8Xq/wYokaaA==" saltValue="wOVbQdE/SvwKoC9YTBLGsQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/RM.xlsx
+++ b/RM.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KANU\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C55A6EE-1959-4619-98D2-9D50612FC7A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8235"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5023" uniqueCount="2600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5072" uniqueCount="2625">
   <si>
     <t>ID</t>
   </si>
@@ -6483,7 +6484,9 @@
   <si>
     <t>Used for:
 MP0372.1
-MP0368.1</t>
+MP0368.1
+MP0397.1
+MP0447.1</t>
   </si>
   <si>
     <t>RM006.5</t>
@@ -8389,11 +8392,90 @@
   <si>
     <t>Product: CP-BG-CHIPS-XX-B; Grade: Flex-PET TM</t>
   </si>
+  <si>
+    <t>RM276</t>
+  </si>
+  <si>
+    <t>63mm Neck 21gm ROPP</t>
+  </si>
+  <si>
+    <t>RM276.1</t>
+  </si>
+  <si>
+    <t>Pet Preform 63mm 21gm Clear TPAC</t>
+  </si>
+  <si>
+    <t>RM272.2</t>
+  </si>
+  <si>
+    <t>Pet Preform 53mm 29gm Amber TPAC</t>
+  </si>
+  <si>
+    <t>RM277</t>
+  </si>
+  <si>
+    <t>96mm/100mm Neck 58gm ROPP</t>
+  </si>
+  <si>
+    <t>RM277.1</t>
+  </si>
+  <si>
+    <t>Pet Preform 96mm/100mm 58gm Clear TPAC</t>
+  </si>
+  <si>
+    <t>RM278</t>
+  </si>
+  <si>
+    <t>Borolab Green</t>
+  </si>
+  <si>
+    <t>RM278.1</t>
+  </si>
+  <si>
+    <t>Borolab Green MB PP</t>
+  </si>
+  <si>
+    <t>MASTER BATCH GREEN</t>
+  </si>
+  <si>
+    <t>Shiv Shakti Industry</t>
+  </si>
+  <si>
+    <t>RM191.3</t>
+  </si>
+  <si>
+    <t>LDPE Bag 25, 750mm (W) * 550mm (L) SP</t>
+  </si>
+  <si>
+    <t>RM078.13</t>
+  </si>
+  <si>
+    <t>FTC Long 19mm Lotion Pink (3mm) ACE H=29.0, OD=22.6, W=3.0</t>
+  </si>
+  <si>
+    <t>To be procured....
+Codification basis: PO</t>
+  </si>
+  <si>
+    <t>RM213.4</t>
+  </si>
+  <si>
+    <t>CRC Cap 38mm Milky White VP</t>
+  </si>
+  <si>
+    <t>Child Lock Cap 38mm White</t>
+  </si>
+  <si>
+    <t>Height: 17.35 mm (with Engraving)
+            16.90 mm (w/o engraving)
+Weight: 7.11 gm - 7.25 gm
+OD: 44.70 mm - 45.00 mm</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -8544,39 +8626,41 @@
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="15">
     <dxf>
       <font>
         <b/>
@@ -8591,9 +8675,9 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -8613,23 +8697,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -8650,99 +8717,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -8789,21 +8763,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -8828,21 +8787,28 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -8867,21 +8833,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -8906,21 +8857,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -8945,21 +8881,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -8984,22 +8905,30 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
@@ -9050,24 +8979,6 @@
         </bottom>
       </border>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -9082,20 +8993,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:K567" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
-  <autoFilter ref="A1:K567"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BA53CF36-EE4E-4E61-BD5F-8F797DCA75A2}" name="Table1" displayName="Table1" ref="A1:K574" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
+  <autoFilter ref="A1:K574" xr:uid="{BA53CF36-EE4E-4E61-BD5F-8F797DCA75A2}"/>
   <tableColumns count="11">
-    <tableColumn id="1" name="ID" dataDxfId="11"/>
-    <tableColumn id="2" name="Status" dataDxfId="10"/>
-    <tableColumn id="3" name="Material List::Material_Detail" dataDxfId="9"/>
-    <tableColumn id="4" name="Product_Code" dataDxfId="8"/>
-    <tableColumn id="5" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
-    <tableColumn id="6" name="Item_Code" dataDxfId="6"/>
-    <tableColumn id="7" name="Old_Item_Code" dataDxfId="5"/>
-    <tableColumn id="8" name="Item_Name" dataDxfId="4"/>
-    <tableColumn id="9" name="Item_Detail_by_Vendor" dataDxfId="3"/>
-    <tableColumn id="10" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
-    <tableColumn id="11" name="Remarks" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{273BA412-44EF-41D3-A3F5-E258F4DB6200}" name="ID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{89BC743C-756B-47ED-BC5D-5E999780A857}" name="Status" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{C312064B-711A-4907-B874-4A04B902031D}" name="Material List::Material_Detail" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{C5C29848-09EB-4CCC-A5D2-A78037490A93}" name="Product_Code" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{82E56AE4-111A-4E04-BA77-3147105E0FCF}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{25406663-880F-4386-A268-4440AD2C42DB}" name="Item_Code" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{D78125CA-BBED-42EF-A272-58E17F4C974E}" name="Old_Item_Code" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{64D80203-1485-4E54-B01C-F07CD3834B16}" name="Item_Name" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{DA98E6CE-B191-42BF-881A-86D0ED8FE3FF}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{251E5C14-AD60-4316-B0EB-26950D7F35C7}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{442C33CE-FD02-461C-B415-50B8128523BA}" name="Remarks" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9118,7 +9029,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -9130,7 +9041,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -9147,9 +9058,9 @@
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -9177,14 +9088,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -9212,6 +9140,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -9363,8 +9308,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K567"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K574"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -27899,38 +27844,241 @@
       </c>
     </row>
     <row r="567" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A567" s="9">
+      <c r="A567" s="4">
         <v>567</v>
       </c>
-      <c r="B567" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C567" s="10" t="s">
+      <c r="B567" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C567" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D567" s="10" t="s">
+      <c r="D567" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E567" s="10" t="s">
+      <c r="E567" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F567" s="10" t="s">
+      <c r="F567" s="5" t="s">
         <v>2597</v>
       </c>
-      <c r="G567" s="11"/>
-      <c r="H567" s="10" t="s">
+      <c r="G567" s="7"/>
+      <c r="H567" s="5" t="s">
         <v>2598</v>
       </c>
-      <c r="I567" s="10" t="s">
+      <c r="I567" s="5" t="s">
         <v>2599</v>
       </c>
-      <c r="J567" s="10" t="s">
+      <c r="J567" s="5" t="s">
         <v>2171</v>
       </c>
-      <c r="K567" s="12"/>
+      <c r="K567" s="6"/>
+    </row>
+    <row r="568" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A568" s="4">
+        <v>568</v>
+      </c>
+      <c r="B568" s="7"/>
+      <c r="C568" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="D568" s="5" t="s">
+        <v>2600</v>
+      </c>
+      <c r="E568" s="5" t="s">
+        <v>2601</v>
+      </c>
+      <c r="F568" s="5" t="s">
+        <v>2602</v>
+      </c>
+      <c r="G568" s="7"/>
+      <c r="H568" s="5" t="s">
+        <v>2603</v>
+      </c>
+      <c r="I568" s="7"/>
+      <c r="J568" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="K568" s="6"/>
+    </row>
+    <row r="569" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A569" s="4">
+        <v>569</v>
+      </c>
+      <c r="B569" s="7"/>
+      <c r="C569" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="D569" s="5" t="s">
+        <v>2556</v>
+      </c>
+      <c r="E569" s="5" t="s">
+        <v>2557</v>
+      </c>
+      <c r="F569" s="5" t="s">
+        <v>2604</v>
+      </c>
+      <c r="G569" s="7"/>
+      <c r="H569" s="5" t="s">
+        <v>2605</v>
+      </c>
+      <c r="I569" s="7"/>
+      <c r="J569" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="K569" s="6"/>
+    </row>
+    <row r="570" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A570" s="4">
+        <v>570</v>
+      </c>
+      <c r="B570" s="7"/>
+      <c r="C570" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="D570" s="5" t="s">
+        <v>2606</v>
+      </c>
+      <c r="E570" s="5" t="s">
+        <v>2607</v>
+      </c>
+      <c r="F570" s="5" t="s">
+        <v>2608</v>
+      </c>
+      <c r="G570" s="7"/>
+      <c r="H570" s="5" t="s">
+        <v>2609</v>
+      </c>
+      <c r="I570" s="7"/>
+      <c r="J570" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="K570" s="6"/>
+    </row>
+    <row r="571" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A571" s="4">
+        <v>571</v>
+      </c>
+      <c r="B571" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C571" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="D571" s="5" t="s">
+        <v>2610</v>
+      </c>
+      <c r="E571" s="5" t="s">
+        <v>2611</v>
+      </c>
+      <c r="F571" s="5" t="s">
+        <v>2612</v>
+      </c>
+      <c r="G571" s="7"/>
+      <c r="H571" s="5" t="s">
+        <v>2613</v>
+      </c>
+      <c r="I571" s="5" t="s">
+        <v>2614</v>
+      </c>
+      <c r="J571" s="5" t="s">
+        <v>2615</v>
+      </c>
+      <c r="K571" s="6"/>
+    </row>
+    <row r="572" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A572" s="4">
+        <v>572</v>
+      </c>
+      <c r="B572" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C572" s="5" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D572" s="5" t="s">
+        <v>1361</v>
+      </c>
+      <c r="E572" s="5" t="s">
+        <v>1362</v>
+      </c>
+      <c r="F572" s="5" t="s">
+        <v>2616</v>
+      </c>
+      <c r="G572" s="7"/>
+      <c r="H572" s="5" t="s">
+        <v>2617</v>
+      </c>
+      <c r="I572" s="7"/>
+      <c r="J572" s="5" t="s">
+        <v>851</v>
+      </c>
+      <c r="K572" s="6"/>
+    </row>
+    <row r="573" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A573" s="4">
+        <v>573</v>
+      </c>
+      <c r="B573" s="7"/>
+      <c r="C573" s="5" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D573" s="5" t="s">
+        <v>1473</v>
+      </c>
+      <c r="E573" s="5" t="s">
+        <v>1474</v>
+      </c>
+      <c r="F573" s="5" t="s">
+        <v>2618</v>
+      </c>
+      <c r="G573" s="7"/>
+      <c r="H573" s="5" t="s">
+        <v>2619</v>
+      </c>
+      <c r="I573" s="7"/>
+      <c r="J573" s="5" t="s">
+        <v>1669</v>
+      </c>
+      <c r="K573" s="8" t="s">
+        <v>2620</v>
+      </c>
+    </row>
+    <row r="574" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A574" s="9">
+        <v>574</v>
+      </c>
+      <c r="B574" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C574" s="10" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D574" s="10" t="s">
+        <v>1930</v>
+      </c>
+      <c r="E574" s="10" t="s">
+        <v>1931</v>
+      </c>
+      <c r="F574" s="10" t="s">
+        <v>2621</v>
+      </c>
+      <c r="G574" s="11"/>
+      <c r="H574" s="10" t="s">
+        <v>2622</v>
+      </c>
+      <c r="I574" s="10" t="s">
+        <v>2623</v>
+      </c>
+      <c r="J574" s="10" t="s">
+        <v>1786</v>
+      </c>
+      <c r="K574" s="12" t="s">
+        <v>2624</v>
+      </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="/gdxXmsyrUy0Xgpr/aQXcP9UR6tHGKp4EZH1tUgRDZ25wnJNXa0FrZsrRWuruiCYpnzzNrbLrMl8Xq/wYokaaA==" saltValue="wOVbQdE/SvwKoC9YTBLGsQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="RFZYJQIJ1R47kFb9TU8Cb8cpxJrK9NRHaoGByOW6x5VvLPVnidZtBMttvuHfnN2KkUt6UDBAJa90tAkLxS398Q==" saltValue="qiVH2vcYBuwU4iIKoSINWw==" spinCount="100000" sheet="1" objects="1" scenarios="1" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/RM.xlsx
+++ b/RM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C55A6EE-1959-4619-98D2-9D50612FC7A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A23EB5BD-ED0B-4992-9E55-E4BB98B95FB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5072" uniqueCount="2625">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5078" uniqueCount="2630">
   <si>
     <t>ID</t>
   </si>
@@ -8375,13 +8375,15 @@
     <t>RM087.8</t>
   </si>
   <si>
-    <t>Screw 53mm Black Short Cap</t>
+    <t>Screw 53mm Black Short Cap UC</t>
   </si>
   <si>
     <t>ULTRA 53MM JAR CAP (BLACK)</t>
   </si>
   <si>
-    <t>TO BE PROCURED........</t>
+    <t>Height: 14.40 mm
+Weight: 3.65 gm - 4.00 gm
+OD: 54.50 mm</t>
   </si>
   <si>
     <t>RM002.18</t>
@@ -8470,6 +8472,21 @@
             16.90 mm (w/o engraving)
 Weight: 7.11 gm - 7.25 gm
 OD: 44.70 mm - 45.00 mm</t>
+  </si>
+  <si>
+    <t>RM279</t>
+  </si>
+  <si>
+    <t>FTC 38mm Half Flip H=17.80, OD=39.60, W=3.80</t>
+  </si>
+  <si>
+    <t>RM279.1</t>
+  </si>
+  <si>
+    <t>FTC 38mm Half Flip Milky White</t>
+  </si>
+  <si>
+    <t>Codification Basis: One Sample Pc from MD SIR</t>
   </si>
 </sst>
 </file>
@@ -8649,10 +8666,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -8660,7 +8677,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="16">
     <dxf>
       <font>
         <b/>
@@ -8697,6 +8714,8 @@
       </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -8979,6 +8998,9 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -8993,20 +9015,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BA53CF36-EE4E-4E61-BD5F-8F797DCA75A2}" name="Table1" displayName="Table1" ref="A1:K574" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
-  <autoFilter ref="A1:K574" xr:uid="{BA53CF36-EE4E-4E61-BD5F-8F797DCA75A2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2778F695-4FC3-4B30-9EC4-C181E68C07EE}" name="Table1" displayName="Table1" ref="A1:K575" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
+  <autoFilter ref="A1:K575" xr:uid="{2778F695-4FC3-4B30-9EC4-C181E68C07EE}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{273BA412-44EF-41D3-A3F5-E258F4DB6200}" name="ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{89BC743C-756B-47ED-BC5D-5E999780A857}" name="Status" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{C312064B-711A-4907-B874-4A04B902031D}" name="Material List::Material_Detail" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{C5C29848-09EB-4CCC-A5D2-A78037490A93}" name="Product_Code" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{82E56AE4-111A-4E04-BA77-3147105E0FCF}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{25406663-880F-4386-A268-4440AD2C42DB}" name="Item_Code" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{D78125CA-BBED-42EF-A272-58E17F4C974E}" name="Old_Item_Code" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{64D80203-1485-4E54-B01C-F07CD3834B16}" name="Item_Name" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{DA98E6CE-B191-42BF-881A-86D0ED8FE3FF}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{251E5C14-AD60-4316-B0EB-26950D7F35C7}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{442C33CE-FD02-461C-B415-50B8128523BA}" name="Remarks" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{623F42CB-984E-482C-AE13-6AFFC4D1D5CE}" name="ID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{D5D0B65C-F934-4813-9505-60BB0AC9EBAE}" name="Status" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{6CCFC986-7F6E-4C21-BE99-2AEB40198890}" name="Material List::Material_Detail" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{C1A86E80-A73F-4FF6-B87D-596AA0992AE9}" name="Product_Code" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{1CE499F9-06C0-466C-89BA-BC3C52970EB5}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{94F91DAA-AD9E-42A2-BDD4-3D3F8C3F0176}" name="Item_Code" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{63C9BF75-ECFE-4D20-B68C-87C9DE388B0B}" name="Old_Item_Code" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{2A14D89A-E532-41E4-A7CA-93CEF42CD641}" name="Item_Name" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{EA187A61-B3EA-4D2E-BB16-7E303FDA5576}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{3350D2AA-DA7C-4EF3-A9D2-42B6B7063E76}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{E1598331-2A9B-49FE-88B7-68A949715C0A}" name="Remarks" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9309,7 +9331,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K574"/>
+  <dimension ref="A1:K575"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -28045,40 +28067,67 @@
       </c>
     </row>
     <row r="574" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A574" s="9">
+      <c r="A574" s="4">
         <v>574</v>
       </c>
-      <c r="B574" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C574" s="10" t="s">
+      <c r="B574" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C574" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="D574" s="10" t="s">
+      <c r="D574" s="5" t="s">
         <v>1930</v>
       </c>
-      <c r="E574" s="10" t="s">
+      <c r="E574" s="5" t="s">
         <v>1931</v>
       </c>
-      <c r="F574" s="10" t="s">
+      <c r="F574" s="5" t="s">
         <v>2621</v>
       </c>
-      <c r="G574" s="11"/>
-      <c r="H574" s="10" t="s">
+      <c r="G574" s="7"/>
+      <c r="H574" s="5" t="s">
         <v>2622</v>
       </c>
-      <c r="I574" s="10" t="s">
+      <c r="I574" s="5" t="s">
         <v>2623</v>
       </c>
-      <c r="J574" s="10" t="s">
+      <c r="J574" s="5" t="s">
         <v>1786</v>
       </c>
-      <c r="K574" s="12" t="s">
+      <c r="K574" s="8" t="s">
         <v>2624</v>
       </c>
     </row>
+    <row r="575" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A575" s="9">
+        <v>575</v>
+      </c>
+      <c r="B575" s="10"/>
+      <c r="C575" s="11" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D575" s="11" t="s">
+        <v>2625</v>
+      </c>
+      <c r="E575" s="11" t="s">
+        <v>2626</v>
+      </c>
+      <c r="F575" s="11" t="s">
+        <v>2627</v>
+      </c>
+      <c r="G575" s="10"/>
+      <c r="H575" s="11" t="s">
+        <v>2628</v>
+      </c>
+      <c r="I575" s="10"/>
+      <c r="J575" s="10"/>
+      <c r="K575" s="12" t="s">
+        <v>2629</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="RFZYJQIJ1R47kFb9TU8Cb8cpxJrK9NRHaoGByOW6x5VvLPVnidZtBMttvuHfnN2KkUt6UDBAJa90tAkLxS398Q==" saltValue="qiVH2vcYBuwU4iIKoSINWw==" spinCount="100000" sheet="1" objects="1" scenarios="1" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="BrefJekzLBpD8g51cp3SYQE7/z2psfnYxT0glbKRzX8uVn9PwkRA0lvzv4qXfT55rm5W3OSmOfU2qPGku6Zfkg==" saltValue="x2hr42WoLqthR+X0z/fWDg==" spinCount="100000" sheet="1" objects="1" scenarios="1" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/RM.xlsx
+++ b/RM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A23EB5BD-ED0B-4992-9E55-E4BB98B95FB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CEB3941-0B1D-40D5-8D6C-9BE20E1BC16B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5078" uniqueCount="2630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5101" uniqueCount="2642">
   <si>
     <t>ID</t>
   </si>
@@ -4651,7 +4651,10 @@
   </si>
   <si>
     <t>Packing Detail for 4000Pcs ( 4 x 1000Pcs per Packet) per Box:
-BOX: RM161.1 (5652CB)</t>
+BOX: RM161.1 (5652CB)
+Dia.: 24.50 mm
+Thickness: 1.50 mm
+Weight: 0.18 gm</t>
   </si>
   <si>
     <t>RM199</t>
@@ -5402,6 +5405,12 @@
     <t>Screw 28mm BMW Green Cap</t>
   </si>
   <si>
+    <t>EP LINER USED:
+Dia.: 27.50 mm
+Weight: 0.19 gm
+Thickness: 1.30 mm</t>
+  </si>
+  <si>
     <t>RM201.1</t>
   </si>
   <si>
@@ -5479,7 +5488,11 @@
   <si>
     <t>Total Height: 22.40 mm
 OD: 32.50 mm
-Weight: 3.40 gm</t>
+Weight: 3.40 gm
+EP LINER USED:
+Dia.: 27.50 mm
+Weight: 0.19 gm
+Thickness: 1.30 mm</t>
   </si>
   <si>
     <t>RM083.3</t>
@@ -7676,7 +7689,9 @@
 Dia: 5.90 mm
 Wall Thickness: 0.66 mm
 Pipe Weight: 1.87 gm
-ARTWORK: STOP, OPEN</t>
+ARTWORK: STOP, OPEN
+also
+CLOSE, OPEN (Pic Attached in Collage)</t>
   </si>
   <si>
     <t>RM239.3</t>
@@ -7685,8 +7700,15 @@
     <t>FTC 24mm Jasmine Blue Short (5mm) ACE</t>
   </si>
   <si>
+    <t>24mm Short Fliptop Cap J Blue 5000</t>
+  </si>
+  <si>
     <t>To be procured....
-Codification done prior purchase.</t>
+Codification done prior purchase.
+Weight: 3.45 gm
+Height: 22.20 mm
+Pourer ID: 5.00 mm
+OD(Mouth): 26.80 mm</t>
   </si>
   <si>
     <t>RM111.12</t>
@@ -7695,8 +7717,15 @@
     <t>FTC Short 19mm Dark Pearl Pink (3mm) ACE</t>
   </si>
   <si>
+    <t>19mm Short Fliptop Cap DP Pink 7500</t>
+  </si>
+  <si>
     <t>Codification done prior purchase.
-Procured on: 13 Jan 2026</t>
+Procured on: 13 Jan 2026
+Weight: 2.60 gm
+Height: 23.80 mm
+Pourer ID: 3.00 mm
+OD(Mouth): 22.45 mm</t>
   </si>
   <si>
     <t>RM262.2</t>
@@ -7797,6 +7826,10 @@
   </si>
   <si>
     <t>Yellow DMB/U3/251127/5495/D1</t>
+  </si>
+  <si>
+    <t>To be procured....
+Codification done prior purchase.</t>
   </si>
   <si>
     <t>RM266</t>
@@ -8486,7 +8519,36 @@
     <t>FTC 38mm Half Flip Milky White</t>
   </si>
   <si>
-    <t>Codification Basis: One Sample Pc from MD SIR</t>
+    <t>Codification Basis: One Sample Pc from MD SIR, Vendor not final yet</t>
+  </si>
+  <si>
+    <t>RM082.6</t>
+  </si>
+  <si>
+    <t>FTC Medium 24mm White (3mm) ACE H=31.50, OD=27.20, W=4.50</t>
+  </si>
+  <si>
+    <t>24mm Long Fliptop Cap White 3600</t>
+  </si>
+  <si>
+    <t>Height: 31.30 mm
+Weight: 4.65 gm
+OD: 27.28 mm</t>
+  </si>
+  <si>
+    <t>RM111.15</t>
+  </si>
+  <si>
+    <t>FTC Short 19mm Red (3mm) ACE H=23.8, OD=22.4, W=2.68</t>
+  </si>
+  <si>
+    <t>19mm Short Fliptop Cap Red 7500</t>
+  </si>
+  <si>
+    <t>Weight: 2.68 gm
+Height: 23.80 mm
+Pourer ID: 3.00 mm
+OD(Mouth): 22.48 mm</t>
   </si>
 </sst>
 </file>
@@ -8666,10 +8728,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -8760,6 +8822,8 @@
       </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -9015,20 +9079,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2778F695-4FC3-4B30-9EC4-C181E68C07EE}" name="Table1" displayName="Table1" ref="A1:K575" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
-  <autoFilter ref="A1:K575" xr:uid="{2778F695-4FC3-4B30-9EC4-C181E68C07EE}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CB691F95-0A1C-4692-8B8B-1D0A40B9B473}" name="Table1" displayName="Table1" ref="A1:K577" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
+  <autoFilter ref="A1:K577" xr:uid="{CB691F95-0A1C-4692-8B8B-1D0A40B9B473}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{623F42CB-984E-482C-AE13-6AFFC4D1D5CE}" name="ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{D5D0B65C-F934-4813-9505-60BB0AC9EBAE}" name="Status" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{6CCFC986-7F6E-4C21-BE99-2AEB40198890}" name="Material List::Material_Detail" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{C1A86E80-A73F-4FF6-B87D-596AA0992AE9}" name="Product_Code" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{1CE499F9-06C0-466C-89BA-BC3C52970EB5}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{94F91DAA-AD9E-42A2-BDD4-3D3F8C3F0176}" name="Item_Code" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{63C9BF75-ECFE-4D20-B68C-87C9DE388B0B}" name="Old_Item_Code" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{2A14D89A-E532-41E4-A7CA-93CEF42CD641}" name="Item_Name" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{EA187A61-B3EA-4D2E-BB16-7E303FDA5576}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{3350D2AA-DA7C-4EF3-A9D2-42B6B7063E76}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{E1598331-2A9B-49FE-88B7-68A949715C0A}" name="Remarks" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{933C9A43-83B4-4237-8C82-B92A49062887}" name="ID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{F7E718B2-ABD8-4A7C-979E-D2AE8AE50F4A}" name="Status" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{346A97BB-8D1C-4B2F-B6CB-B46126ABAB59}" name="Material List::Material_Detail" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{C743BD7A-D8A3-4650-915C-F338688B3A33}" name="Product_Code" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{F895AC09-2AB0-448D-8B67-F0158E16A7B5}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{F0254111-B0B6-4399-994A-6C9A0FB03B47}" name="Item_Code" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{B0A13EF6-C57C-4EA3-B440-43FC1ACB43C7}" name="Old_Item_Code" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{0E3E2A44-6890-43A7-9102-8A3A6599DF77}" name="Item_Name" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{76E54F0B-4253-4F26-A255-232797CB8A61}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{8A507C32-61FE-4198-BA49-7F9573311229}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{9C0C3A41-8807-4B1B-BD4D-1A3EFD5301DE}" name="Remarks" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9331,7 +9395,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K575"/>
+  <dimension ref="A1:K577"/>
   <sheetFormatPr defaultColWidth="21.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" bestFit="1" customWidth="1"/>
@@ -21624,7 +21688,9 @@
       <c r="J371" s="5" t="s">
         <v>1524</v>
       </c>
-      <c r="K371" s="6"/>
+      <c r="K371" s="8" t="s">
+        <v>1775</v>
+      </c>
     </row>
     <row r="372" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A372" s="4">
@@ -21643,14 +21709,14 @@
         <v>1541</v>
       </c>
       <c r="F372" s="5" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="G372" s="7"/>
       <c r="H372" s="5" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="I372" s="5" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="J372" s="5" t="s">
         <v>1524</v>
@@ -21668,20 +21734,20 @@
         <v>1472</v>
       </c>
       <c r="D373" s="5" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="E373" s="5" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="F373" s="5" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="G373" s="7"/>
       <c r="H373" s="5" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="I373" s="5" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="J373" s="5" t="s">
         <v>1524</v>
@@ -21705,17 +21771,17 @@
         <v>1570</v>
       </c>
       <c r="F374" s="5" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="G374" s="7"/>
       <c r="H374" s="5" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="I374" s="5" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="J374" s="5" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="K374" s="6"/>
     </row>
@@ -21736,14 +21802,14 @@
         <v>1576</v>
       </c>
       <c r="F375" s="5" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="G375" s="7"/>
       <c r="H375" s="5" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="I375" s="5" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="J375" s="5" t="s">
         <v>1496</v>
@@ -21767,20 +21833,20 @@
         <v>1474</v>
       </c>
       <c r="F376" s="5" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="G376" s="7"/>
       <c r="H376" s="5" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="I376" s="5" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="J376" s="5" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="K376" s="8" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="377" spans="1:11" x14ac:dyDescent="0.2">
@@ -21800,20 +21866,20 @@
         <v>1474</v>
       </c>
       <c r="F377" s="5" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="G377" s="7"/>
       <c r="H377" s="5" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="I377" s="5" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="J377" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K377" s="8" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="378" spans="1:11" x14ac:dyDescent="0.2">
@@ -21833,20 +21899,20 @@
         <v>1554</v>
       </c>
       <c r="F378" s="5" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="G378" s="7"/>
       <c r="H378" s="5" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="I378" s="5" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="J378" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K378" s="8" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="379" spans="1:11" x14ac:dyDescent="0.2">
@@ -21866,17 +21932,17 @@
         <v>1570</v>
       </c>
       <c r="F379" s="5" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="G379" s="7"/>
       <c r="H379" s="5" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="I379" s="5" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="J379" s="5" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="K379" s="6"/>
     </row>
@@ -21897,20 +21963,20 @@
         <v>1576</v>
       </c>
       <c r="F380" s="5" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="G380" s="7"/>
       <c r="H380" s="5" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="I380" s="5" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="J380" s="5" t="s">
         <v>1479</v>
       </c>
       <c r="K380" s="8" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="381" spans="1:11" x14ac:dyDescent="0.2">
@@ -21930,17 +21996,17 @@
         <v>1570</v>
       </c>
       <c r="F381" s="5" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="G381" s="7"/>
       <c r="H381" s="5" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="I381" s="5" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="J381" s="5" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="K381" s="6"/>
     </row>
@@ -21961,20 +22027,20 @@
         <v>1033</v>
       </c>
       <c r="F382" s="5" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="G382" s="7"/>
       <c r="H382" s="5" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="I382" s="5" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="J382" s="5" t="s">
         <v>1013</v>
       </c>
       <c r="K382" s="8" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="383" spans="1:11" x14ac:dyDescent="0.2">
@@ -21994,20 +22060,20 @@
         <v>122</v>
       </c>
       <c r="F383" s="5" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="G383" s="7"/>
       <c r="H383" s="5" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="I383" s="5" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="J383" s="5" t="s">
         <v>104</v>
       </c>
       <c r="K383" s="8" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="384" spans="1:11" x14ac:dyDescent="0.2">
@@ -22021,20 +22087,20 @@
         <v>1287</v>
       </c>
       <c r="D384" s="5" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="E384" s="5" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="F384" s="5" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="G384" s="7"/>
       <c r="H384" s="5" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="I384" s="5" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="J384" s="5" t="s">
         <v>1005</v>
@@ -22058,20 +22124,20 @@
         <v>1570</v>
       </c>
       <c r="F385" s="5" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="G385" s="7"/>
       <c r="H385" s="5" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="I385" s="5" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="J385" s="5" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="K385" s="8" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="386" spans="1:11" x14ac:dyDescent="0.2">
@@ -22091,14 +22157,14 @@
         <v>122</v>
       </c>
       <c r="F386" s="5" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="G386" s="7"/>
       <c r="H386" s="5" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="I386" s="5" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="J386" s="5" t="s">
         <v>104</v>
@@ -22116,20 +22182,20 @@
         <v>12</v>
       </c>
       <c r="D387" s="5" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="E387" s="5" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="F387" s="5" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="G387" s="7"/>
       <c r="H387" s="5" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="I387" s="5" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="J387" s="5" t="s">
         <v>19</v>
@@ -22144,29 +22210,29 @@
         <v>11</v>
       </c>
       <c r="C388" s="5" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="D388" s="5" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="E388" s="5" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="F388" s="5" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="G388" s="7"/>
       <c r="H388" s="5" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="I388" s="5" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="J388" s="5" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="K388" s="8" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="389" spans="1:11" x14ac:dyDescent="0.2">
@@ -22180,20 +22246,20 @@
         <v>67</v>
       </c>
       <c r="D389" s="5" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="E389" s="5" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="F389" s="5" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="G389" s="7"/>
       <c r="H389" s="5" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="I389" s="5" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="J389" s="5" t="s">
         <v>223</v>
@@ -22217,17 +22283,17 @@
         <v>1570</v>
       </c>
       <c r="F390" s="5" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="G390" s="7"/>
       <c r="H390" s="5" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="I390" s="5" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="J390" s="5" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="K390" s="6"/>
     </row>
@@ -22248,14 +22314,14 @@
         <v>1737</v>
       </c>
       <c r="F391" s="5" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="G391" s="7"/>
       <c r="H391" s="5" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="I391" s="5" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="J391" s="5" t="s">
         <v>1524</v>
@@ -22279,20 +22345,20 @@
         <v>1648</v>
       </c>
       <c r="F392" s="5" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="G392" s="7"/>
       <c r="H392" s="5" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="I392" s="5" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="J392" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K392" s="8" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="393" spans="1:11" x14ac:dyDescent="0.2">
@@ -22306,26 +22372,26 @@
         <v>1472</v>
       </c>
       <c r="D393" s="5" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="E393" s="5" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="F393" s="5" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="G393" s="7"/>
       <c r="H393" s="5" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="I393" s="5" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="J393" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K393" s="8" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="394" spans="1:11" x14ac:dyDescent="0.2">
@@ -22345,20 +22411,20 @@
         <v>1533</v>
       </c>
       <c r="F394" s="5" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="G394" s="7"/>
       <c r="H394" s="5" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="I394" s="5" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="J394" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K394" s="8" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="395" spans="1:11" x14ac:dyDescent="0.2">
@@ -22372,20 +22438,20 @@
         <v>1472</v>
       </c>
       <c r="D395" s="5" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="E395" s="5" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="F395" s="5" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="G395" s="7"/>
       <c r="H395" s="5" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="I395" s="5" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="J395" s="5" t="s">
         <v>1524</v>
@@ -22403,20 +22469,20 @@
         <v>1472</v>
       </c>
       <c r="D396" s="5" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="E396" s="5" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="F396" s="5" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="G396" s="7"/>
       <c r="H396" s="5" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="I396" s="5" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="J396" s="5" t="s">
         <v>1524</v>
@@ -22431,29 +22497,29 @@
         <v>11</v>
       </c>
       <c r="C397" s="5" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="D397" s="5" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="E397" s="5" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="F397" s="5" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="G397" s="7"/>
       <c r="H397" s="5" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="I397" s="5" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="J397" s="5" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="K397" s="8" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="398" spans="1:11" x14ac:dyDescent="0.2">
@@ -22467,26 +22533,26 @@
         <v>277</v>
       </c>
       <c r="D398" s="5" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="E398" s="5" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="F398" s="5" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="G398" s="7"/>
       <c r="H398" s="5" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="I398" s="5" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="J398" s="5" t="s">
         <v>283</v>
       </c>
       <c r="K398" s="8" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="399" spans="1:11" x14ac:dyDescent="0.2">
@@ -22506,7 +22572,7 @@
         <v>1352</v>
       </c>
       <c r="F399" s="5" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="G399" s="7"/>
       <c r="H399" s="5" t="s">
@@ -22537,20 +22603,20 @@
         <v>1637</v>
       </c>
       <c r="F400" s="5" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="G400" s="7"/>
       <c r="H400" s="5" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="I400" s="5" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="J400" s="5" t="s">
         <v>1669</v>
       </c>
       <c r="K400" s="8" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="401" spans="1:11" x14ac:dyDescent="0.2">
@@ -22570,20 +22636,20 @@
         <v>1637</v>
       </c>
       <c r="F401" s="5" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="G401" s="7"/>
       <c r="H401" s="5" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="I401" s="5" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="J401" s="5" t="s">
         <v>1669</v>
       </c>
       <c r="K401" s="8" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="402" spans="1:11" x14ac:dyDescent="0.2">
@@ -22603,20 +22669,20 @@
         <v>1648</v>
       </c>
       <c r="F402" s="5" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
       <c r="G402" s="7"/>
       <c r="H402" s="5" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="I402" s="5" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
       <c r="J402" s="5" t="s">
         <v>1669</v>
       </c>
       <c r="K402" s="8" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="403" spans="1:11" x14ac:dyDescent="0.2">
@@ -22636,20 +22702,20 @@
         <v>1648</v>
       </c>
       <c r="F403" s="5" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="G403" s="7"/>
       <c r="H403" s="5" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="I403" s="5" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="J403" s="5" t="s">
         <v>1669</v>
       </c>
       <c r="K403" s="8" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="404" spans="1:11" x14ac:dyDescent="0.2">
@@ -22669,14 +22735,14 @@
         <v>1519</v>
       </c>
       <c r="F404" s="5" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="G404" s="7"/>
       <c r="H404" s="5" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="I404" s="5" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="J404" s="5" t="s">
         <v>1524</v>
@@ -22694,26 +22760,26 @@
         <v>588</v>
       </c>
       <c r="D405" s="5" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="E405" s="5" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="F405" s="5" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="G405" s="7"/>
       <c r="H405" s="5" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="I405" s="5" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="J405" s="5" t="s">
         <v>619</v>
       </c>
       <c r="K405" s="8" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="406" spans="1:11" x14ac:dyDescent="0.2">
@@ -22727,20 +22793,20 @@
         <v>1472</v>
       </c>
       <c r="D406" s="5" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="E406" s="5" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="F406" s="5" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="G406" s="7"/>
       <c r="H406" s="5" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="I406" s="5" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="J406" s="5" t="s">
         <v>619</v>
@@ -22758,26 +22824,26 @@
         <v>1287</v>
       </c>
       <c r="D407" s="5" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="E407" s="5" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="F407" s="5" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="G407" s="7"/>
       <c r="H407" s="5" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="I407" s="5" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="J407" s="5" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="K407" s="8" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="408" spans="1:11" x14ac:dyDescent="0.2">
@@ -22797,14 +22863,14 @@
         <v>760</v>
       </c>
       <c r="F408" s="5" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="G408" s="7"/>
       <c r="H408" s="5" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="I408" s="5" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="J408" s="5" t="s">
         <v>619</v>
@@ -22822,26 +22888,26 @@
         <v>67</v>
       </c>
       <c r="D409" s="5" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="E409" s="5" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="F409" s="5" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="G409" s="7"/>
       <c r="H409" s="5" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="I409" s="5" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="J409" s="5" t="s">
         <v>177</v>
       </c>
       <c r="K409" s="8" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="410" spans="1:11" x14ac:dyDescent="0.2">
@@ -22855,26 +22921,26 @@
         <v>1472</v>
       </c>
       <c r="D410" s="5" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="E410" s="5" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="F410" s="5" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="G410" s="7"/>
       <c r="H410" s="5" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="I410" s="5" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="J410" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K410" s="8" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="411" spans="1:11" x14ac:dyDescent="0.2">
@@ -22888,26 +22954,26 @@
         <v>277</v>
       </c>
       <c r="D411" s="5" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="E411" s="5" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="F411" s="5" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="G411" s="7"/>
       <c r="H411" s="5" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="I411" s="5" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="J411" s="5" t="s">
         <v>283</v>
       </c>
       <c r="K411" s="8" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="412" spans="1:11" x14ac:dyDescent="0.2">
@@ -22921,24 +22987,24 @@
         <v>1472</v>
       </c>
       <c r="D412" s="5" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="E412" s="5" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="F412" s="5" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="G412" s="7"/>
       <c r="H412" s="5" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="I412" s="7"/>
       <c r="J412" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K412" s="8" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="413" spans="1:11" x14ac:dyDescent="0.2">
@@ -22952,26 +23018,26 @@
         <v>1287</v>
       </c>
       <c r="D413" s="5" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="E413" s="5" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="F413" s="5" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="G413" s="7"/>
       <c r="H413" s="5" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="I413" s="5" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="J413" s="5" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="K413" s="8" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="414" spans="1:11" x14ac:dyDescent="0.2">
@@ -22991,20 +23057,20 @@
         <v>627</v>
       </c>
       <c r="F414" s="5" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="G414" s="7"/>
       <c r="H414" s="5" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="I414" s="5" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="J414" s="5" t="s">
         <v>619</v>
       </c>
       <c r="K414" s="8" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="415" spans="1:11" x14ac:dyDescent="0.2">
@@ -23024,20 +23090,20 @@
         <v>46</v>
       </c>
       <c r="F415" s="5" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="G415" s="7"/>
       <c r="H415" s="5" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="I415" s="5" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="J415" s="5" t="s">
         <v>51</v>
       </c>
       <c r="K415" s="8" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="416" spans="1:11" x14ac:dyDescent="0.2">
@@ -23057,20 +23123,20 @@
         <v>1637</v>
       </c>
       <c r="F416" s="5" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="G416" s="7"/>
       <c r="H416" s="5" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="I416" s="5" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="J416" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K416" s="8" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="417" spans="1:11" x14ac:dyDescent="0.2">
@@ -23084,26 +23150,26 @@
         <v>1287</v>
       </c>
       <c r="D417" s="5" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="E417" s="5" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="F417" s="5" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="G417" s="7"/>
       <c r="H417" s="5" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="I417" s="5" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="J417" s="5" t="s">
         <v>851</v>
       </c>
       <c r="K417" s="8" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="418" spans="1:11" x14ac:dyDescent="0.2">
@@ -23123,20 +23189,20 @@
         <v>25</v>
       </c>
       <c r="F418" s="5" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="G418" s="7"/>
       <c r="H418" s="5" t="s">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="I418" s="5" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="J418" s="5" t="s">
         <v>34</v>
       </c>
       <c r="K418" s="8" t="s">
-        <v>1961</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="419" spans="1:11" x14ac:dyDescent="0.2">
@@ -23156,20 +23222,20 @@
         <v>627</v>
       </c>
       <c r="F419" s="5" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="G419" s="7"/>
       <c r="H419" s="5" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="I419" s="5" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="J419" s="5" t="s">
         <v>619</v>
       </c>
       <c r="K419" s="8" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="420" spans="1:11" x14ac:dyDescent="0.2">
@@ -23189,20 +23255,20 @@
         <v>627</v>
       </c>
       <c r="F420" s="5" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="G420" s="7"/>
       <c r="H420" s="5" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="I420" s="5" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="J420" s="5" t="s">
         <v>619</v>
       </c>
       <c r="K420" s="8" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="421" spans="1:11" x14ac:dyDescent="0.2">
@@ -23216,26 +23282,26 @@
         <v>1287</v>
       </c>
       <c r="D421" s="5" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="E421" s="5" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="F421" s="5" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="G421" s="7"/>
       <c r="H421" s="5" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="I421" s="5" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="J421" s="5" t="s">
         <v>1444</v>
       </c>
       <c r="K421" s="8" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
     </row>
     <row r="422" spans="1:11" x14ac:dyDescent="0.2">
@@ -23249,24 +23315,24 @@
         <v>1287</v>
       </c>
       <c r="D422" s="5" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="E422" s="5" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="F422" s="5" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="G422" s="7"/>
       <c r="H422" s="5" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="I422" s="7"/>
       <c r="J422" s="5" t="s">
         <v>1444</v>
       </c>
       <c r="K422" s="8" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="423" spans="1:11" x14ac:dyDescent="0.2">
@@ -23286,20 +23352,20 @@
         <v>25</v>
       </c>
       <c r="F423" s="5" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="G423" s="7"/>
       <c r="H423" s="5" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="I423" s="5" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="J423" s="5" t="s">
         <v>34</v>
       </c>
       <c r="K423" s="8" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="424" spans="1:11" x14ac:dyDescent="0.2">
@@ -23313,17 +23379,17 @@
         <v>1472</v>
       </c>
       <c r="D424" s="5" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="E424" s="5" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="F424" s="5" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="G424" s="7"/>
       <c r="H424" s="5" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="I424" s="5" t="s">
         <v>1551</v>
@@ -23332,7 +23398,7 @@
         <v>1552</v>
       </c>
       <c r="K424" s="8" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
     </row>
     <row r="425" spans="1:11" x14ac:dyDescent="0.2">
@@ -23346,13 +23412,13 @@
         <v>1472</v>
       </c>
       <c r="D425" s="5" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="E425" s="5" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="F425" s="5" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="G425" s="7"/>
       <c r="H425" s="5" t="s">
@@ -23377,23 +23443,23 @@
         <v>1472</v>
       </c>
       <c r="D426" s="5" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="E426" s="5" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="F426" s="5" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="G426" s="7"/>
       <c r="H426" s="5" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="I426" s="5" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="J426" s="5" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="K426" s="6"/>
     </row>
@@ -23414,7 +23480,7 @@
         <v>1294</v>
       </c>
       <c r="F427" s="5" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="G427" s="7"/>
       <c r="H427" s="5" t="s">
@@ -23443,11 +23509,11 @@
         <v>1289</v>
       </c>
       <c r="F428" s="5" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="G428" s="7"/>
       <c r="H428" s="5" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="I428" s="7"/>
       <c r="J428" s="5" t="s">
@@ -23472,7 +23538,7 @@
         <v>1294</v>
       </c>
       <c r="F429" s="5" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="G429" s="7"/>
       <c r="H429" s="5" t="s">
@@ -23501,7 +23567,7 @@
         <v>1299</v>
       </c>
       <c r="F430" s="5" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="G430" s="7"/>
       <c r="H430" s="5" t="s">
@@ -23512,7 +23578,7 @@
         <v>851</v>
       </c>
       <c r="K430" s="8" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="431" spans="1:11" x14ac:dyDescent="0.2">
@@ -23532,11 +23598,11 @@
         <v>1299</v>
       </c>
       <c r="F431" s="5" t="s">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="G431" s="7"/>
       <c r="H431" s="5" t="s">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="I431" s="7"/>
       <c r="J431" s="5" t="s">
@@ -23555,26 +23621,26 @@
         <v>588</v>
       </c>
       <c r="D432" s="5" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="E432" s="5" t="s">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="F432" s="5" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="G432" s="7"/>
       <c r="H432" s="5" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="I432" s="5" t="s">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="J432" s="5" t="s">
         <v>641</v>
       </c>
       <c r="K432" s="8" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="433" spans="1:11" x14ac:dyDescent="0.2">
@@ -23585,29 +23651,29 @@
         <v>11</v>
       </c>
       <c r="C433" s="5" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="D433" s="5" t="s">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="E433" s="5" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="F433" s="5" t="s">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="G433" s="7"/>
       <c r="H433" s="5" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="I433" s="5" t="s">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="J433" s="5" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="K433" s="8" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="434" spans="1:11" x14ac:dyDescent="0.2">
@@ -23621,26 +23687,26 @@
         <v>588</v>
       </c>
       <c r="D434" s="5" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="E434" s="5" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="F434" s="5" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="G434" s="7"/>
       <c r="H434" s="5" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="I434" s="5" t="s">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="J434" s="5" t="s">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="K434" s="8" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="435" spans="1:11" x14ac:dyDescent="0.2">
@@ -23660,20 +23726,20 @@
         <v>25</v>
       </c>
       <c r="F435" s="5" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="G435" s="7"/>
       <c r="H435" s="5" t="s">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="I435" s="5" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="J435" s="5" t="s">
         <v>34</v>
       </c>
       <c r="K435" s="8" t="s">
-        <v>2021</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="436" spans="1:11" x14ac:dyDescent="0.2">
@@ -23687,26 +23753,26 @@
         <v>765</v>
       </c>
       <c r="D436" s="5" t="s">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E436" s="5" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F436" s="5" t="s">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G436" s="7"/>
       <c r="H436" s="5" t="s">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="I436" s="5" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="J436" s="5" t="s">
         <v>797</v>
       </c>
       <c r="K436" s="8" t="s">
-        <v>2027</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="437" spans="1:11" x14ac:dyDescent="0.2">
@@ -23726,20 +23792,20 @@
         <v>1715</v>
       </c>
       <c r="F437" s="5" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="G437" s="7"/>
       <c r="H437" s="5" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="I437" s="5" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="J437" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K437" s="8" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="438" spans="1:11" x14ac:dyDescent="0.2">
@@ -23759,20 +23825,20 @@
         <v>1737</v>
       </c>
       <c r="F438" s="5" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="G438" s="7"/>
       <c r="H438" s="5" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="I438" s="5" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="J438" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K438" s="8" t="s">
-        <v>2035</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="439" spans="1:11" x14ac:dyDescent="0.2">
@@ -23792,20 +23858,20 @@
         <v>1327</v>
       </c>
       <c r="F439" s="5" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="G439" s="7"/>
       <c r="H439" s="5" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="I439" s="5" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="J439" s="5" t="s">
         <v>851</v>
       </c>
       <c r="K439" s="8" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="440" spans="1:11" x14ac:dyDescent="0.2">
@@ -23819,26 +23885,26 @@
         <v>1472</v>
       </c>
       <c r="D440" s="5" t="s">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="E440" s="5" t="s">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="F440" s="5" t="s">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="G440" s="7"/>
       <c r="H440" s="5" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="I440" s="5" t="s">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="J440" s="5" t="s">
         <v>1479</v>
       </c>
       <c r="K440" s="8" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="441" spans="1:11" x14ac:dyDescent="0.2">
@@ -23852,26 +23918,26 @@
         <v>588</v>
       </c>
       <c r="D441" s="5" t="s">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="E441" s="5" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="F441" s="5" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="G441" s="7"/>
       <c r="H441" s="5" t="s">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="I441" s="5" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="J441" s="5" t="s">
         <v>619</v>
       </c>
       <c r="K441" s="8" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="442" spans="1:11" x14ac:dyDescent="0.2">
@@ -23891,20 +23957,20 @@
         <v>1474</v>
       </c>
       <c r="F442" s="5" t="s">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="G442" s="7"/>
       <c r="H442" s="5" t="s">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="I442" s="5" t="s">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="J442" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K442" s="8" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="443" spans="1:11" x14ac:dyDescent="0.2">
@@ -23918,26 +23984,26 @@
         <v>1472</v>
       </c>
       <c r="D443" s="5" t="s">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="E443" s="5" t="s">
-        <v>2057</v>
+        <v>2058</v>
       </c>
       <c r="F443" s="5" t="s">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="G443" s="7"/>
       <c r="H443" s="5" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="I443" s="5" t="s">
-        <v>2060</v>
+        <v>2061</v>
       </c>
       <c r="J443" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K443" s="8" t="s">
-        <v>2061</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="444" spans="1:11" x14ac:dyDescent="0.2">
@@ -23951,26 +24017,26 @@
         <v>765</v>
       </c>
       <c r="D444" s="5" t="s">
-        <v>2062</v>
+        <v>2063</v>
       </c>
       <c r="E444" s="5" t="s">
-        <v>2063</v>
+        <v>2064</v>
       </c>
       <c r="F444" s="5" t="s">
-        <v>2064</v>
+        <v>2065</v>
       </c>
       <c r="G444" s="7"/>
       <c r="H444" s="5" t="s">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="I444" s="5" t="s">
-        <v>2066</v>
+        <v>2067</v>
       </c>
       <c r="J444" s="5" t="s">
         <v>797</v>
       </c>
       <c r="K444" s="8" t="s">
-        <v>2067</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="445" spans="1:11" x14ac:dyDescent="0.2">
@@ -23984,26 +24050,26 @@
         <v>969</v>
       </c>
       <c r="D445" s="5" t="s">
-        <v>2068</v>
+        <v>2069</v>
       </c>
       <c r="E445" s="5" t="s">
-        <v>2069</v>
+        <v>2070</v>
       </c>
       <c r="F445" s="5" t="s">
-        <v>2070</v>
+        <v>2071</v>
       </c>
       <c r="G445" s="7"/>
       <c r="H445" s="5" t="s">
-        <v>2071</v>
+        <v>2072</v>
       </c>
       <c r="I445" s="5" t="s">
-        <v>2072</v>
+        <v>2073</v>
       </c>
       <c r="J445" s="5" t="s">
         <v>1005</v>
       </c>
       <c r="K445" s="8" t="s">
-        <v>2073</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="446" spans="1:11" x14ac:dyDescent="0.2">
@@ -24023,18 +24089,18 @@
         <v>1519</v>
       </c>
       <c r="F446" s="5" t="s">
-        <v>2074</v>
+        <v>2075</v>
       </c>
       <c r="G446" s="7"/>
       <c r="H446" s="5" t="s">
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="I446" s="7"/>
       <c r="J446" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K446" s="8" t="s">
-        <v>2076</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="447" spans="1:11" x14ac:dyDescent="0.2">
@@ -24054,20 +24120,20 @@
         <v>1637</v>
       </c>
       <c r="F447" s="5" t="s">
-        <v>2077</v>
+        <v>2078</v>
       </c>
       <c r="G447" s="7"/>
       <c r="H447" s="5" t="s">
-        <v>2078</v>
+        <v>2079</v>
       </c>
       <c r="I447" s="5" t="s">
-        <v>2079</v>
+        <v>2080</v>
       </c>
       <c r="J447" s="5" t="s">
         <v>1669</v>
       </c>
       <c r="K447" s="8" t="s">
-        <v>2080</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="448" spans="1:11" x14ac:dyDescent="0.2">
@@ -24087,20 +24153,20 @@
         <v>1498</v>
       </c>
       <c r="F448" s="5" t="s">
-        <v>2081</v>
+        <v>2082</v>
       </c>
       <c r="G448" s="7"/>
       <c r="H448" s="5" t="s">
-        <v>2082</v>
+        <v>2083</v>
       </c>
       <c r="I448" s="5" t="s">
-        <v>2083</v>
+        <v>2084</v>
       </c>
       <c r="J448" s="5" t="s">
         <v>1669</v>
       </c>
       <c r="K448" s="8" t="s">
-        <v>2084</v>
+        <v>2085</v>
       </c>
     </row>
     <row r="449" spans="1:11" x14ac:dyDescent="0.2">
@@ -24114,26 +24180,26 @@
         <v>588</v>
       </c>
       <c r="D449" s="5" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="E449" s="5" t="s">
-        <v>2086</v>
+        <v>2087</v>
       </c>
       <c r="F449" s="5" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="G449" s="7"/>
       <c r="H449" s="5" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
       <c r="I449" s="5" t="s">
-        <v>2089</v>
+        <v>2090</v>
       </c>
       <c r="J449" s="5" t="s">
         <v>619</v>
       </c>
       <c r="K449" s="8" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="450" spans="1:11" x14ac:dyDescent="0.2">
@@ -24153,20 +24219,20 @@
         <v>62</v>
       </c>
       <c r="F450" s="5" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="G450" s="7"/>
       <c r="H450" s="5" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="I450" s="5" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="J450" s="5" t="s">
-        <v>2094</v>
+        <v>2095</v>
       </c>
       <c r="K450" s="8" t="s">
-        <v>2095</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="451" spans="1:11" x14ac:dyDescent="0.2">
@@ -24180,26 +24246,26 @@
         <v>1472</v>
       </c>
       <c r="D451" s="5" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
       <c r="E451" s="5" t="s">
-        <v>2097</v>
+        <v>2098</v>
       </c>
       <c r="F451" s="5" t="s">
-        <v>2098</v>
+        <v>2099</v>
       </c>
       <c r="G451" s="7"/>
       <c r="H451" s="5" t="s">
-        <v>2099</v>
+        <v>2100</v>
       </c>
       <c r="I451" s="5" t="s">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="J451" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K451" s="8" t="s">
-        <v>2101</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="452" spans="1:11" x14ac:dyDescent="0.2">
@@ -24211,24 +24277,24 @@
         <v>1472</v>
       </c>
       <c r="D452" s="5" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
       <c r="E452" s="5" t="s">
-        <v>2097</v>
+        <v>2098</v>
       </c>
       <c r="F452" s="5" t="s">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="G452" s="7"/>
       <c r="H452" s="5" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
       <c r="I452" s="7"/>
       <c r="J452" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K452" s="8" t="s">
-        <v>2104</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="453" spans="1:11" x14ac:dyDescent="0.2">
@@ -24240,24 +24306,24 @@
         <v>1472</v>
       </c>
       <c r="D453" s="5" t="s">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="E453" s="5" t="s">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="F453" s="5" t="s">
-        <v>2107</v>
+        <v>2108</v>
       </c>
       <c r="G453" s="7"/>
       <c r="H453" s="5" t="s">
-        <v>2108</v>
+        <v>2109</v>
       </c>
       <c r="I453" s="7"/>
       <c r="J453" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K453" s="8" t="s">
-        <v>2104</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="454" spans="1:11" x14ac:dyDescent="0.2">
@@ -24269,24 +24335,24 @@
         <v>1472</v>
       </c>
       <c r="D454" s="5" t="s">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="E454" s="5" t="s">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="F454" s="5" t="s">
-        <v>2109</v>
+        <v>2110</v>
       </c>
       <c r="G454" s="7"/>
       <c r="H454" s="5" t="s">
-        <v>2110</v>
+        <v>2111</v>
       </c>
       <c r="I454" s="7"/>
       <c r="J454" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K454" s="8" t="s">
-        <v>2111</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="455" spans="1:11" x14ac:dyDescent="0.2">
@@ -24298,24 +24364,24 @@
         <v>1472</v>
       </c>
       <c r="D455" s="5" t="s">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="E455" s="5" t="s">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="F455" s="5" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="G455" s="7"/>
       <c r="H455" s="5" t="s">
-        <v>2113</v>
+        <v>2114</v>
       </c>
       <c r="I455" s="7"/>
       <c r="J455" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K455" s="8" t="s">
-        <v>2104</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="456" spans="1:11" x14ac:dyDescent="0.2">
@@ -24327,24 +24393,24 @@
         <v>1472</v>
       </c>
       <c r="D456" s="5" t="s">
-        <v>2114</v>
+        <v>2115</v>
       </c>
       <c r="E456" s="5" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="F456" s="5" t="s">
-        <v>2116</v>
+        <v>2117</v>
       </c>
       <c r="G456" s="7"/>
       <c r="H456" s="5" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
       <c r="I456" s="7"/>
       <c r="J456" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K456" s="8" t="s">
-        <v>2104</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="457" spans="1:11" x14ac:dyDescent="0.2">
@@ -24358,26 +24424,26 @@
         <v>1472</v>
       </c>
       <c r="D457" s="5" t="s">
-        <v>2118</v>
+        <v>2119</v>
       </c>
       <c r="E457" s="5" t="s">
-        <v>2119</v>
+        <v>2120</v>
       </c>
       <c r="F457" s="5" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
       <c r="G457" s="7"/>
       <c r="H457" s="5" t="s">
-        <v>2121</v>
+        <v>2122</v>
       </c>
       <c r="I457" s="5" t="s">
-        <v>2122</v>
+        <v>2123</v>
       </c>
       <c r="J457" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K457" s="8" t="s">
-        <v>2123</v>
+        <v>2124</v>
       </c>
     </row>
     <row r="458" spans="1:11" x14ac:dyDescent="0.2">
@@ -24397,20 +24463,20 @@
         <v>62</v>
       </c>
       <c r="F458" s="5" t="s">
-        <v>2124</v>
+        <v>2125</v>
       </c>
       <c r="G458" s="7"/>
       <c r="H458" s="5" t="s">
-        <v>2125</v>
+        <v>2126</v>
       </c>
       <c r="I458" s="5" t="s">
-        <v>2126</v>
+        <v>2127</v>
       </c>
       <c r="J458" s="5" t="s">
         <v>485</v>
       </c>
       <c r="K458" s="8" t="s">
-        <v>2127</v>
+        <v>2128</v>
       </c>
     </row>
     <row r="459" spans="1:11" x14ac:dyDescent="0.2">
@@ -24430,20 +24496,20 @@
         <v>669</v>
       </c>
       <c r="F459" s="5" t="s">
-        <v>2128</v>
+        <v>2129</v>
       </c>
       <c r="G459" s="7"/>
       <c r="H459" s="5" t="s">
-        <v>2129</v>
+        <v>2130</v>
       </c>
       <c r="I459" s="5" t="s">
-        <v>2130</v>
+        <v>2131</v>
       </c>
       <c r="J459" s="5" t="s">
-        <v>2131</v>
+        <v>2132</v>
       </c>
       <c r="K459" s="8" t="s">
-        <v>2132</v>
+        <v>2133</v>
       </c>
     </row>
     <row r="460" spans="1:11" x14ac:dyDescent="0.2">
@@ -24457,26 +24523,26 @@
         <v>588</v>
       </c>
       <c r="D460" s="5" t="s">
-        <v>2133</v>
+        <v>2134</v>
       </c>
       <c r="E460" s="5" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="F460" s="5" t="s">
-        <v>2135</v>
+        <v>2136</v>
       </c>
       <c r="G460" s="7"/>
       <c r="H460" s="5" t="s">
-        <v>2136</v>
+        <v>2137</v>
       </c>
       <c r="I460" s="5" t="s">
-        <v>2137</v>
+        <v>2138</v>
       </c>
       <c r="J460" s="5" t="s">
-        <v>2131</v>
+        <v>2132</v>
       </c>
       <c r="K460" s="8" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="461" spans="1:11" x14ac:dyDescent="0.2">
@@ -24490,26 +24556,26 @@
         <v>588</v>
       </c>
       <c r="D461" s="5" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="E461" s="5" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="F461" s="5" t="s">
-        <v>2139</v>
+        <v>2140</v>
       </c>
       <c r="G461" s="7"/>
       <c r="H461" s="5" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="I461" s="5" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="J461" s="5" t="s">
-        <v>2131</v>
+        <v>2132</v>
       </c>
       <c r="K461" s="8" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="462" spans="1:11" x14ac:dyDescent="0.2">
@@ -24523,24 +24589,24 @@
         <v>1472</v>
       </c>
       <c r="D462" s="5" t="s">
-        <v>2143</v>
+        <v>2144</v>
       </c>
       <c r="E462" s="5" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
       <c r="F462" s="5" t="s">
-        <v>2145</v>
+        <v>2146</v>
       </c>
       <c r="G462" s="7"/>
       <c r="H462" s="5" t="s">
-        <v>2146</v>
+        <v>2147</v>
       </c>
       <c r="I462" s="7"/>
       <c r="J462" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K462" s="8" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="463" spans="1:11" x14ac:dyDescent="0.2">
@@ -24554,20 +24620,20 @@
         <v>1472</v>
       </c>
       <c r="D463" s="5" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="E463" s="5" t="s">
-        <v>2149</v>
+        <v>2150</v>
       </c>
       <c r="F463" s="5" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
       <c r="G463" s="7"/>
       <c r="H463" s="5" t="s">
-        <v>2151</v>
+        <v>2152</v>
       </c>
       <c r="I463" s="5" t="s">
-        <v>2152</v>
+        <v>2153</v>
       </c>
       <c r="J463" s="5" t="s">
         <v>1524</v>
@@ -24585,26 +24651,26 @@
         <v>588</v>
       </c>
       <c r="D464" s="5" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="E464" s="5" t="s">
-        <v>2154</v>
+        <v>2155</v>
       </c>
       <c r="F464" s="5" t="s">
-        <v>2155</v>
+        <v>2156</v>
       </c>
       <c r="G464" s="7"/>
       <c r="H464" s="5" t="s">
-        <v>2156</v>
+        <v>2157</v>
       </c>
       <c r="I464" s="5" t="s">
-        <v>2157</v>
+        <v>2158</v>
       </c>
       <c r="J464" s="5" t="s">
-        <v>2158</v>
+        <v>2159</v>
       </c>
       <c r="K464" s="8" t="s">
-        <v>2159</v>
+        <v>2160</v>
       </c>
     </row>
     <row r="465" spans="1:11" x14ac:dyDescent="0.2">
@@ -24618,20 +24684,20 @@
         <v>1472</v>
       </c>
       <c r="D465" s="5" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="E465" s="5" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="F465" s="5" t="s">
-        <v>2160</v>
+        <v>2161</v>
       </c>
       <c r="G465" s="7"/>
       <c r="H465" s="5" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="I465" s="5" t="s">
-        <v>2162</v>
+        <v>2163</v>
       </c>
       <c r="J465" s="5" t="s">
         <v>1669</v>
@@ -24649,26 +24715,26 @@
         <v>1472</v>
       </c>
       <c r="D466" s="5" t="s">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="E466" s="5" t="s">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="F466" s="5" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="G466" s="7"/>
       <c r="H466" s="5" t="s">
-        <v>2164</v>
+        <v>2165</v>
       </c>
       <c r="I466" s="5" t="s">
-        <v>2165</v>
+        <v>2166</v>
       </c>
       <c r="J466" s="5" t="s">
-        <v>2166</v>
+        <v>2167</v>
       </c>
       <c r="K466" s="8" t="s">
-        <v>2167</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="467" spans="1:11" x14ac:dyDescent="0.2">
@@ -24688,17 +24754,17 @@
         <v>14</v>
       </c>
       <c r="F467" s="5" t="s">
-        <v>2168</v>
+        <v>2169</v>
       </c>
       <c r="G467" s="7"/>
       <c r="H467" s="5" t="s">
-        <v>2169</v>
+        <v>2170</v>
       </c>
       <c r="I467" s="5" t="s">
-        <v>2170</v>
+        <v>2171</v>
       </c>
       <c r="J467" s="5" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
       <c r="K467" s="6"/>
     </row>
@@ -24713,26 +24779,26 @@
         <v>1472</v>
       </c>
       <c r="D468" s="5" t="s">
-        <v>2172</v>
+        <v>2173</v>
       </c>
       <c r="E468" s="5" t="s">
-        <v>2173</v>
+        <v>2174</v>
       </c>
       <c r="F468" s="5" t="s">
-        <v>2174</v>
+        <v>2175</v>
       </c>
       <c r="G468" s="7"/>
       <c r="H468" s="5" t="s">
-        <v>2175</v>
+        <v>2176</v>
       </c>
       <c r="I468" s="5" t="s">
-        <v>2176</v>
+        <v>2177</v>
       </c>
       <c r="J468" s="5" t="s">
         <v>1669</v>
       </c>
       <c r="K468" s="8" t="s">
-        <v>2177</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="469" spans="1:11" x14ac:dyDescent="0.2">
@@ -24746,26 +24812,26 @@
         <v>1472</v>
       </c>
       <c r="D469" s="5" t="s">
-        <v>2172</v>
+        <v>2173</v>
       </c>
       <c r="E469" s="5" t="s">
-        <v>2173</v>
+        <v>2174</v>
       </c>
       <c r="F469" s="5" t="s">
-        <v>2178</v>
+        <v>2179</v>
       </c>
       <c r="G469" s="7"/>
       <c r="H469" s="5" t="s">
-        <v>2179</v>
+        <v>2180</v>
       </c>
       <c r="I469" s="5" t="s">
-        <v>2180</v>
+        <v>2181</v>
       </c>
       <c r="J469" s="5" t="s">
         <v>1669</v>
       </c>
       <c r="K469" s="8" t="s">
-        <v>2181</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="470" spans="1:11" x14ac:dyDescent="0.2">
@@ -24779,26 +24845,26 @@
         <v>765</v>
       </c>
       <c r="D470" s="5" t="s">
-        <v>2182</v>
+        <v>2183</v>
       </c>
       <c r="E470" s="5" t="s">
-        <v>2183</v>
+        <v>2184</v>
       </c>
       <c r="F470" s="5" t="s">
-        <v>2184</v>
+        <v>2185</v>
       </c>
       <c r="G470" s="7"/>
       <c r="H470" s="5" t="s">
-        <v>2185</v>
+        <v>2186</v>
       </c>
       <c r="I470" s="5" t="s">
-        <v>2186</v>
+        <v>2187</v>
       </c>
       <c r="J470" s="5" t="s">
         <v>797</v>
       </c>
       <c r="K470" s="8" t="s">
-        <v>2187</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="471" spans="1:11" x14ac:dyDescent="0.2">
@@ -24818,11 +24884,11 @@
         <v>1322</v>
       </c>
       <c r="F471" s="5" t="s">
-        <v>2188</v>
+        <v>2189</v>
       </c>
       <c r="G471" s="7"/>
       <c r="H471" s="5" t="s">
-        <v>2189</v>
+        <v>2190</v>
       </c>
       <c r="I471" s="5" t="s">
         <v>1287</v>
@@ -24849,11 +24915,11 @@
         <v>1294</v>
       </c>
       <c r="F472" s="5" t="s">
-        <v>2190</v>
+        <v>2191</v>
       </c>
       <c r="G472" s="7"/>
       <c r="H472" s="5" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="I472" s="5" t="s">
         <v>1287</v>
@@ -24880,11 +24946,11 @@
         <v>1299</v>
       </c>
       <c r="F473" s="5" t="s">
-        <v>2192</v>
+        <v>2193</v>
       </c>
       <c r="G473" s="7"/>
       <c r="H473" s="5" t="s">
-        <v>2193</v>
+        <v>2194</v>
       </c>
       <c r="I473" s="5" t="s">
         <v>1287</v>
@@ -24911,14 +24977,14 @@
         <v>736</v>
       </c>
       <c r="F474" s="5" t="s">
-        <v>2194</v>
+        <v>2195</v>
       </c>
       <c r="G474" s="7"/>
       <c r="H474" s="5" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="I474" s="5" t="s">
-        <v>2196</v>
+        <v>2197</v>
       </c>
       <c r="J474" s="5" t="s">
         <v>619</v>
@@ -24936,26 +25002,26 @@
         <v>12</v>
       </c>
       <c r="D475" s="5" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="E475" s="5" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="F475" s="5" t="s">
-        <v>2197</v>
+        <v>2198</v>
       </c>
       <c r="G475" s="7"/>
       <c r="H475" s="5" t="s">
-        <v>2198</v>
+        <v>2199</v>
       </c>
       <c r="I475" s="5" t="s">
-        <v>2199</v>
+        <v>2200</v>
       </c>
       <c r="J475" s="5" t="s">
-        <v>2200</v>
+        <v>2201</v>
       </c>
       <c r="K475" s="8" t="s">
-        <v>2201</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="476" spans="1:11" x14ac:dyDescent="0.2">
@@ -24969,26 +25035,26 @@
         <v>12</v>
       </c>
       <c r="D476" s="5" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="E476" s="5" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="F476" s="5" t="s">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="G476" s="7"/>
       <c r="H476" s="5" t="s">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="I476" s="5" t="s">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="J476" s="5" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
       <c r="K476" s="8" t="s">
-        <v>2206</v>
+        <v>2207</v>
       </c>
     </row>
     <row r="477" spans="1:11" x14ac:dyDescent="0.2">
@@ -25002,26 +25068,26 @@
         <v>588</v>
       </c>
       <c r="D477" s="5" t="s">
-        <v>2207</v>
+        <v>2208</v>
       </c>
       <c r="E477" s="5" t="s">
-        <v>2208</v>
+        <v>2209</v>
       </c>
       <c r="F477" s="5" t="s">
-        <v>2209</v>
+        <v>2210</v>
       </c>
       <c r="G477" s="7"/>
       <c r="H477" s="5" t="s">
-        <v>2210</v>
+        <v>2211</v>
       </c>
       <c r="I477" s="5" t="s">
-        <v>2211</v>
+        <v>2212</v>
       </c>
       <c r="J477" s="5" t="s">
-        <v>2212</v>
+        <v>2213</v>
       </c>
       <c r="K477" s="8" t="s">
-        <v>2213</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="478" spans="1:11" x14ac:dyDescent="0.2">
@@ -25035,20 +25101,20 @@
         <v>1472</v>
       </c>
       <c r="D478" s="5" t="s">
-        <v>2214</v>
+        <v>2215</v>
       </c>
       <c r="E478" s="5" t="s">
-        <v>2215</v>
+        <v>2216</v>
       </c>
       <c r="F478" s="5" t="s">
-        <v>2216</v>
+        <v>2217</v>
       </c>
       <c r="G478" s="7"/>
       <c r="H478" s="5" t="s">
-        <v>2217</v>
+        <v>2218</v>
       </c>
       <c r="I478" s="5" t="s">
-        <v>2218</v>
+        <v>2219</v>
       </c>
       <c r="J478" s="5" t="s">
         <v>1587</v>
@@ -25072,7 +25138,7 @@
         <v>1307</v>
       </c>
       <c r="F479" s="5" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="G479" s="7"/>
       <c r="H479" s="5" t="s">
@@ -25083,7 +25149,7 @@
         <v>1005</v>
       </c>
       <c r="K479" s="8" t="s">
-        <v>2220</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="480" spans="1:11" x14ac:dyDescent="0.2">
@@ -25103,20 +25169,20 @@
         <v>767</v>
       </c>
       <c r="F480" s="5" t="s">
-        <v>2221</v>
+        <v>2222</v>
       </c>
       <c r="G480" s="7"/>
       <c r="H480" s="5" t="s">
-        <v>2222</v>
+        <v>2223</v>
       </c>
       <c r="I480" s="5" t="s">
-        <v>2223</v>
+        <v>2224</v>
       </c>
       <c r="J480" s="5" t="s">
-        <v>2224</v>
+        <v>2225</v>
       </c>
       <c r="K480" s="8" t="s">
-        <v>2225</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="481" spans="1:11" x14ac:dyDescent="0.2">
@@ -25136,20 +25202,20 @@
         <v>774</v>
       </c>
       <c r="F481" s="5" t="s">
-        <v>2226</v>
+        <v>2227</v>
       </c>
       <c r="G481" s="7"/>
       <c r="H481" s="5" t="s">
         <v>777</v>
       </c>
       <c r="I481" s="5" t="s">
-        <v>2227</v>
+        <v>2228</v>
       </c>
       <c r="J481" s="5" t="s">
-        <v>2224</v>
+        <v>2225</v>
       </c>
       <c r="K481" s="8" t="s">
-        <v>2228</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="482" spans="1:11" x14ac:dyDescent="0.2">
@@ -25169,14 +25235,14 @@
         <v>1307</v>
       </c>
       <c r="F482" s="5" t="s">
-        <v>2229</v>
+        <v>2230</v>
       </c>
       <c r="G482" s="7"/>
       <c r="H482" s="5" t="s">
         <v>1449</v>
       </c>
       <c r="I482" s="5" t="s">
-        <v>2230</v>
+        <v>2231</v>
       </c>
       <c r="J482" s="5" t="s">
         <v>851</v>
@@ -25194,26 +25260,26 @@
         <v>1472</v>
       </c>
       <c r="D483" s="5" t="s">
-        <v>2231</v>
+        <v>2232</v>
       </c>
       <c r="E483" s="5" t="s">
-        <v>2232</v>
+        <v>2233</v>
       </c>
       <c r="F483" s="5" t="s">
-        <v>2233</v>
+        <v>2234</v>
       </c>
       <c r="G483" s="7"/>
       <c r="H483" s="5" t="s">
-        <v>2234</v>
+        <v>2235</v>
       </c>
       <c r="I483" s="5" t="s">
-        <v>2235</v>
+        <v>2236</v>
       </c>
       <c r="J483" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K483" s="8" t="s">
-        <v>2236</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="484" spans="1:11" x14ac:dyDescent="0.2">
@@ -25227,26 +25293,26 @@
         <v>1472</v>
       </c>
       <c r="D484" s="5" t="s">
-        <v>2237</v>
+        <v>2238</v>
       </c>
       <c r="E484" s="5" t="s">
-        <v>2238</v>
+        <v>2239</v>
       </c>
       <c r="F484" s="5" t="s">
-        <v>2239</v>
+        <v>2240</v>
       </c>
       <c r="G484" s="7"/>
       <c r="H484" s="5" t="s">
-        <v>2240</v>
+        <v>2241</v>
       </c>
       <c r="I484" s="5" t="s">
-        <v>2241</v>
+        <v>2242</v>
       </c>
       <c r="J484" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K484" s="8" t="s">
-        <v>2242</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="485" spans="1:11" x14ac:dyDescent="0.2">
@@ -25260,20 +25326,20 @@
         <v>1472</v>
       </c>
       <c r="D485" s="5" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="E485" s="5" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="F485" s="5" t="s">
-        <v>2243</v>
+        <v>2244</v>
       </c>
       <c r="G485" s="7"/>
       <c r="H485" s="5" t="s">
-        <v>2244</v>
+        <v>2245</v>
       </c>
       <c r="I485" s="5" t="s">
-        <v>2245</v>
+        <v>2246</v>
       </c>
       <c r="J485" s="5" t="s">
         <v>1669</v>
@@ -25291,20 +25357,20 @@
         <v>1472</v>
       </c>
       <c r="D486" s="5" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="E486" s="5" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="F486" s="5" t="s">
-        <v>2246</v>
+        <v>2247</v>
       </c>
       <c r="G486" s="7"/>
       <c r="H486" s="5" t="s">
-        <v>2247</v>
+        <v>2248</v>
       </c>
       <c r="I486" s="5" t="s">
-        <v>2248</v>
+        <v>2249</v>
       </c>
       <c r="J486" s="5" t="s">
         <v>619</v>
@@ -25328,11 +25394,11 @@
         <v>1554</v>
       </c>
       <c r="F487" s="5" t="s">
-        <v>2249</v>
+        <v>2250</v>
       </c>
       <c r="G487" s="7"/>
       <c r="H487" s="5" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
       <c r="I487" s="7"/>
       <c r="J487" s="5" t="s">
@@ -25357,14 +25423,14 @@
         <v>657</v>
       </c>
       <c r="F488" s="5" t="s">
-        <v>2251</v>
+        <v>2252</v>
       </c>
       <c r="G488" s="7"/>
       <c r="H488" s="5" t="s">
-        <v>2252</v>
+        <v>2253</v>
       </c>
       <c r="I488" s="5" t="s">
-        <v>2253</v>
+        <v>2254</v>
       </c>
       <c r="J488" s="5" t="s">
         <v>619</v>
@@ -25388,20 +25454,20 @@
         <v>1648</v>
       </c>
       <c r="F489" s="5" t="s">
-        <v>2254</v>
+        <v>2255</v>
       </c>
       <c r="G489" s="7"/>
       <c r="H489" s="5" t="s">
-        <v>2255</v>
+        <v>2256</v>
       </c>
       <c r="I489" s="5" t="s">
-        <v>2256</v>
+        <v>2257</v>
       </c>
       <c r="J489" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K489" s="8" t="s">
-        <v>2257</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="490" spans="1:11" x14ac:dyDescent="0.2">
@@ -25415,26 +25481,26 @@
         <v>1472</v>
       </c>
       <c r="D490" s="5" t="s">
-        <v>2143</v>
+        <v>2144</v>
       </c>
       <c r="E490" s="5" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
       <c r="F490" s="5" t="s">
-        <v>2258</v>
+        <v>2259</v>
       </c>
       <c r="G490" s="7"/>
       <c r="H490" s="5" t="s">
-        <v>2259</v>
+        <v>2260</v>
       </c>
       <c r="I490" s="5" t="s">
-        <v>2260</v>
+        <v>2261</v>
       </c>
       <c r="J490" s="5" t="s">
-        <v>2166</v>
+        <v>2167</v>
       </c>
       <c r="K490" s="8" t="s">
-        <v>2261</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="491" spans="1:11" x14ac:dyDescent="0.2">
@@ -25448,24 +25514,24 @@
         <v>1006</v>
       </c>
       <c r="D491" s="5" t="s">
-        <v>2262</v>
+        <v>2263</v>
       </c>
       <c r="E491" s="5" t="s">
-        <v>2263</v>
+        <v>2264</v>
       </c>
       <c r="F491" s="5" t="s">
-        <v>2264</v>
+        <v>2265</v>
       </c>
       <c r="G491" s="7"/>
       <c r="H491" s="5" t="s">
-        <v>2265</v>
+        <v>2266</v>
       </c>
       <c r="I491" s="7"/>
       <c r="J491" s="5" t="s">
         <v>1013</v>
       </c>
       <c r="K491" s="8" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="492" spans="1:11" x14ac:dyDescent="0.2">
@@ -25485,14 +25551,14 @@
         <v>14</v>
       </c>
       <c r="F492" s="5" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
       <c r="G492" s="7"/>
       <c r="H492" s="5" t="s">
-        <v>2268</v>
+        <v>2269</v>
       </c>
       <c r="I492" s="5" t="s">
-        <v>2269</v>
+        <v>2270</v>
       </c>
       <c r="J492" s="5" t="s">
         <v>34</v>
@@ -25510,26 +25576,26 @@
         <v>588</v>
       </c>
       <c r="D493" s="5" t="s">
-        <v>2270</v>
+        <v>2271</v>
       </c>
       <c r="E493" s="5" t="s">
-        <v>2271</v>
+        <v>2272</v>
       </c>
       <c r="F493" s="5" t="s">
-        <v>2272</v>
+        <v>2273</v>
       </c>
       <c r="G493" s="7"/>
       <c r="H493" s="5" t="s">
-        <v>2273</v>
+        <v>2274</v>
       </c>
       <c r="I493" s="5" t="s">
-        <v>2274</v>
+        <v>2275</v>
       </c>
       <c r="J493" s="5" t="s">
         <v>641</v>
       </c>
       <c r="K493" s="8" t="s">
-        <v>2275</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="494" spans="1:11" x14ac:dyDescent="0.2">
@@ -25543,23 +25609,23 @@
         <v>277</v>
       </c>
       <c r="D494" s="5" t="s">
-        <v>2276</v>
+        <v>2277</v>
       </c>
       <c r="E494" s="5" t="s">
-        <v>2277</v>
+        <v>2278</v>
       </c>
       <c r="F494" s="5" t="s">
-        <v>2278</v>
+        <v>2279</v>
       </c>
       <c r="G494" s="7"/>
       <c r="H494" s="5" t="s">
-        <v>2279</v>
+        <v>2280</v>
       </c>
       <c r="I494" s="5" t="s">
-        <v>2280</v>
+        <v>2281</v>
       </c>
       <c r="J494" s="5" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
       <c r="K494" s="6"/>
     </row>
@@ -25574,23 +25640,23 @@
         <v>277</v>
       </c>
       <c r="D495" s="5" t="s">
-        <v>2282</v>
+        <v>2283</v>
       </c>
       <c r="E495" s="5" t="s">
-        <v>2283</v>
+        <v>2284</v>
       </c>
       <c r="F495" s="5" t="s">
-        <v>2284</v>
+        <v>2285</v>
       </c>
       <c r="G495" s="7"/>
       <c r="H495" s="5" t="s">
-        <v>2285</v>
+        <v>2286</v>
       </c>
       <c r="I495" s="5" t="s">
-        <v>2286</v>
+        <v>2287</v>
       </c>
       <c r="J495" s="5" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
       <c r="K495" s="6"/>
     </row>
@@ -25605,23 +25671,23 @@
         <v>277</v>
       </c>
       <c r="D496" s="5" t="s">
-        <v>2287</v>
+        <v>2288</v>
       </c>
       <c r="E496" s="5" t="s">
-        <v>2288</v>
+        <v>2289</v>
       </c>
       <c r="F496" s="5" t="s">
-        <v>2289</v>
+        <v>2290</v>
       </c>
       <c r="G496" s="7"/>
       <c r="H496" s="5" t="s">
-        <v>2290</v>
+        <v>2291</v>
       </c>
       <c r="I496" s="5" t="s">
-        <v>2291</v>
+        <v>2292</v>
       </c>
       <c r="J496" s="5" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
       <c r="K496" s="6"/>
     </row>
@@ -25636,23 +25702,23 @@
         <v>277</v>
       </c>
       <c r="D497" s="5" t="s">
-        <v>2292</v>
+        <v>2293</v>
       </c>
       <c r="E497" s="5" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="F497" s="5" t="s">
-        <v>2294</v>
+        <v>2295</v>
       </c>
       <c r="G497" s="7"/>
       <c r="H497" s="5" t="s">
-        <v>2295</v>
+        <v>2296</v>
       </c>
       <c r="I497" s="5" t="s">
-        <v>2296</v>
+        <v>2297</v>
       </c>
       <c r="J497" s="5" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
       <c r="K497" s="6"/>
     </row>
@@ -25667,23 +25733,23 @@
         <v>277</v>
       </c>
       <c r="D498" s="5" t="s">
-        <v>2297</v>
+        <v>2298</v>
       </c>
       <c r="E498" s="5" t="s">
-        <v>2298</v>
+        <v>2299</v>
       </c>
       <c r="F498" s="5" t="s">
-        <v>2299</v>
+        <v>2300</v>
       </c>
       <c r="G498" s="7"/>
       <c r="H498" s="5" t="s">
-        <v>2300</v>
+        <v>2301</v>
       </c>
       <c r="I498" s="5" t="s">
-        <v>2301</v>
+        <v>2302</v>
       </c>
       <c r="J498" s="5" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
       <c r="K498" s="6"/>
     </row>
@@ -25698,23 +25764,23 @@
         <v>277</v>
       </c>
       <c r="D499" s="5" t="s">
-        <v>2302</v>
+        <v>2303</v>
       </c>
       <c r="E499" s="5" t="s">
-        <v>2303</v>
+        <v>2304</v>
       </c>
       <c r="F499" s="5" t="s">
-        <v>2304</v>
+        <v>2305</v>
       </c>
       <c r="G499" s="7"/>
       <c r="H499" s="5" t="s">
-        <v>2305</v>
+        <v>2306</v>
       </c>
       <c r="I499" s="5" t="s">
-        <v>2306</v>
+        <v>2307</v>
       </c>
       <c r="J499" s="5" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
       <c r="K499" s="6"/>
     </row>
@@ -25729,23 +25795,23 @@
         <v>277</v>
       </c>
       <c r="D500" s="5" t="s">
-        <v>2307</v>
+        <v>2308</v>
       </c>
       <c r="E500" s="5" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
       <c r="F500" s="5" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="G500" s="7"/>
       <c r="H500" s="5" t="s">
-        <v>2310</v>
+        <v>2311</v>
       </c>
       <c r="I500" s="5" t="s">
-        <v>2311</v>
+        <v>2312</v>
       </c>
       <c r="J500" s="5" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
       <c r="K500" s="6"/>
     </row>
@@ -25760,23 +25826,23 @@
         <v>277</v>
       </c>
       <c r="D501" s="5" t="s">
-        <v>2312</v>
+        <v>2313</v>
       </c>
       <c r="E501" s="5" t="s">
-        <v>2313</v>
+        <v>2314</v>
       </c>
       <c r="F501" s="5" t="s">
-        <v>2314</v>
+        <v>2315</v>
       </c>
       <c r="G501" s="7"/>
       <c r="H501" s="5" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="I501" s="5" t="s">
-        <v>2316</v>
+        <v>2317</v>
       </c>
       <c r="J501" s="5" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
       <c r="K501" s="6"/>
     </row>
@@ -25791,26 +25857,26 @@
         <v>588</v>
       </c>
       <c r="D502" s="5" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="E502" s="5" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="F502" s="5" t="s">
-        <v>2317</v>
+        <v>2318</v>
       </c>
       <c r="G502" s="7"/>
       <c r="H502" s="5" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
       <c r="I502" s="5" t="s">
-        <v>2319</v>
+        <v>2320</v>
       </c>
       <c r="J502" s="5" t="s">
         <v>619</v>
       </c>
       <c r="K502" s="8" t="s">
-        <v>2320</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="503" spans="1:11" x14ac:dyDescent="0.2">
@@ -25830,20 +25896,20 @@
         <v>1498</v>
       </c>
       <c r="F503" s="5" t="s">
-        <v>2321</v>
+        <v>2322</v>
       </c>
       <c r="G503" s="7"/>
       <c r="H503" s="5" t="s">
-        <v>2322</v>
+        <v>2323</v>
       </c>
       <c r="I503" s="5" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="J503" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K503" s="8" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="504" spans="1:11" x14ac:dyDescent="0.2">
@@ -25857,26 +25923,26 @@
         <v>588</v>
       </c>
       <c r="D504" s="5" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="E504" s="5" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="F504" s="5" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="G504" s="7"/>
       <c r="H504" s="5" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="I504" s="5" t="s">
-        <v>2326</v>
+        <v>2327</v>
       </c>
       <c r="J504" s="5" t="s">
         <v>619</v>
       </c>
       <c r="K504" s="8" t="s">
-        <v>2327</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="505" spans="1:11" x14ac:dyDescent="0.2">
@@ -25890,26 +25956,26 @@
         <v>765</v>
       </c>
       <c r="D505" s="5" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
       <c r="E505" s="5" t="s">
-        <v>2329</v>
+        <v>2330</v>
       </c>
       <c r="F505" s="5" t="s">
-        <v>2330</v>
+        <v>2331</v>
       </c>
       <c r="G505" s="7"/>
       <c r="H505" s="5" t="s">
-        <v>2331</v>
+        <v>2332</v>
       </c>
       <c r="I505" s="5" t="s">
-        <v>2332</v>
+        <v>2333</v>
       </c>
       <c r="J505" s="5" t="s">
         <v>772</v>
       </c>
       <c r="K505" s="8" t="s">
-        <v>2333</v>
+        <v>2334</v>
       </c>
     </row>
     <row r="506" spans="1:11" x14ac:dyDescent="0.2">
@@ -25929,20 +25995,20 @@
         <v>1737</v>
       </c>
       <c r="F506" s="5" t="s">
-        <v>2334</v>
+        <v>2335</v>
       </c>
       <c r="G506" s="7"/>
       <c r="H506" s="5" t="s">
-        <v>2335</v>
+        <v>2336</v>
       </c>
       <c r="I506" s="5" t="s">
-        <v>2336</v>
+        <v>2337</v>
       </c>
       <c r="J506" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K506" s="8" t="s">
-        <v>2337</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="507" spans="1:11" x14ac:dyDescent="0.2">
@@ -25956,24 +26022,24 @@
         <v>1472</v>
       </c>
       <c r="D507" s="5" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="E507" s="5" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="F507" s="5" t="s">
-        <v>2338</v>
+        <v>2339</v>
       </c>
       <c r="G507" s="7"/>
       <c r="H507" s="5" t="s">
-        <v>2339</v>
+        <v>2340</v>
       </c>
       <c r="I507" s="7"/>
       <c r="J507" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K507" s="8" t="s">
-        <v>2340</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="508" spans="1:11" x14ac:dyDescent="0.2">
@@ -25987,26 +26053,26 @@
         <v>1472</v>
       </c>
       <c r="D508" s="5" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
       <c r="E508" s="5" t="s">
-        <v>2097</v>
+        <v>2098</v>
       </c>
       <c r="F508" s="5" t="s">
-        <v>2341</v>
+        <v>2342</v>
       </c>
       <c r="G508" s="7"/>
       <c r="H508" s="5" t="s">
-        <v>2342</v>
+        <v>2343</v>
       </c>
       <c r="I508" s="5" t="s">
-        <v>2343</v>
+        <v>2344</v>
       </c>
       <c r="J508" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K508" s="8" t="s">
-        <v>2344</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="509" spans="1:11" x14ac:dyDescent="0.2">
@@ -26026,14 +26092,14 @@
         <v>1498</v>
       </c>
       <c r="F509" s="5" t="s">
-        <v>2345</v>
+        <v>2346</v>
       </c>
       <c r="G509" s="7"/>
       <c r="H509" s="5" t="s">
-        <v>2346</v>
+        <v>2347</v>
       </c>
       <c r="I509" s="5" t="s">
-        <v>2347</v>
+        <v>2348</v>
       </c>
       <c r="J509" s="5" t="s">
         <v>1524</v>
@@ -26051,26 +26117,26 @@
         <v>1472</v>
       </c>
       <c r="D510" s="5" t="s">
-        <v>2348</v>
+        <v>2349</v>
       </c>
       <c r="E510" s="5" t="s">
-        <v>2349</v>
+        <v>2350</v>
       </c>
       <c r="F510" s="5" t="s">
-        <v>2350</v>
+        <v>2351</v>
       </c>
       <c r="G510" s="7"/>
       <c r="H510" s="5" t="s">
-        <v>2351</v>
+        <v>2352</v>
       </c>
       <c r="I510" s="5" t="s">
-        <v>2352</v>
+        <v>2353</v>
       </c>
       <c r="J510" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K510" s="8" t="s">
-        <v>2353</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="511" spans="1:11" x14ac:dyDescent="0.2">
@@ -26084,26 +26150,26 @@
         <v>1472</v>
       </c>
       <c r="D511" s="5" t="s">
-        <v>2354</v>
+        <v>2355</v>
       </c>
       <c r="E511" s="5" t="s">
-        <v>2355</v>
+        <v>2356</v>
       </c>
       <c r="F511" s="5" t="s">
-        <v>2356</v>
+        <v>2357</v>
       </c>
       <c r="G511" s="7"/>
       <c r="H511" s="5" t="s">
-        <v>2357</v>
+        <v>2358</v>
       </c>
       <c r="I511" s="5" t="s">
-        <v>2358</v>
+        <v>2359</v>
       </c>
       <c r="J511" s="5" t="s">
         <v>1669</v>
       </c>
       <c r="K511" s="8" t="s">
-        <v>2359</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="512" spans="1:11" x14ac:dyDescent="0.2">
@@ -26123,14 +26189,14 @@
         <v>46</v>
       </c>
       <c r="F512" s="5" t="s">
-        <v>2360</v>
+        <v>2361</v>
       </c>
       <c r="G512" s="7"/>
       <c r="H512" s="5" t="s">
-        <v>2361</v>
+        <v>2362</v>
       </c>
       <c r="I512" s="5" t="s">
-        <v>2362</v>
+        <v>2363</v>
       </c>
       <c r="J512" s="5" t="s">
         <v>485</v>
@@ -26148,26 +26214,26 @@
         <v>1472</v>
       </c>
       <c r="D513" s="5" t="s">
-        <v>2363</v>
+        <v>2364</v>
       </c>
       <c r="E513" s="5" t="s">
-        <v>2364</v>
+        <v>2365</v>
       </c>
       <c r="F513" s="5" t="s">
-        <v>2365</v>
+        <v>2366</v>
       </c>
       <c r="G513" s="7"/>
       <c r="H513" s="5" t="s">
-        <v>2366</v>
+        <v>2367</v>
       </c>
       <c r="I513" s="5" t="s">
-        <v>2366</v>
+        <v>2367</v>
       </c>
       <c r="J513" s="5" t="s">
-        <v>2367</v>
+        <v>2368</v>
       </c>
       <c r="K513" s="8" t="s">
-        <v>2368</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="514" spans="1:11" x14ac:dyDescent="0.2">
@@ -26181,26 +26247,26 @@
         <v>67</v>
       </c>
       <c r="D514" s="5" t="s">
-        <v>2369</v>
+        <v>2370</v>
       </c>
       <c r="E514" s="5" t="s">
-        <v>2370</v>
+        <v>2371</v>
       </c>
       <c r="F514" s="5" t="s">
-        <v>2371</v>
+        <v>2372</v>
       </c>
       <c r="G514" s="7"/>
       <c r="H514" s="5" t="s">
-        <v>2372</v>
+        <v>2373</v>
       </c>
       <c r="I514" s="5" t="s">
-        <v>2373</v>
+        <v>2374</v>
       </c>
       <c r="J514" s="5" t="s">
         <v>223</v>
       </c>
       <c r="K514" s="8" t="s">
-        <v>2374</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="515" spans="1:11" x14ac:dyDescent="0.2">
@@ -26214,26 +26280,26 @@
         <v>67</v>
       </c>
       <c r="D515" s="5" t="s">
-        <v>2375</v>
+        <v>2376</v>
       </c>
       <c r="E515" s="5" t="s">
-        <v>2376</v>
+        <v>2377</v>
       </c>
       <c r="F515" s="5" t="s">
-        <v>2377</v>
+        <v>2378</v>
       </c>
       <c r="G515" s="7"/>
       <c r="H515" s="5" t="s">
-        <v>2378</v>
+        <v>2379</v>
       </c>
       <c r="I515" s="5" t="s">
-        <v>2379</v>
+        <v>2380</v>
       </c>
       <c r="J515" s="5" t="s">
         <v>223</v>
       </c>
       <c r="K515" s="8" t="s">
-        <v>2380</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="516" spans="1:11" x14ac:dyDescent="0.2">
@@ -26253,18 +26319,18 @@
         <v>1637</v>
       </c>
       <c r="F516" s="5" t="s">
-        <v>2381</v>
+        <v>2382</v>
       </c>
       <c r="G516" s="7"/>
       <c r="H516" s="5" t="s">
-        <v>2382</v>
+        <v>2383</v>
       </c>
       <c r="I516" s="7"/>
       <c r="J516" s="5" t="s">
         <v>1669</v>
       </c>
       <c r="K516" s="8" t="s">
-        <v>2383</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="517" spans="1:11" x14ac:dyDescent="0.2">
@@ -26278,24 +26344,24 @@
         <v>1472</v>
       </c>
       <c r="D517" s="5" t="s">
-        <v>2354</v>
+        <v>2355</v>
       </c>
       <c r="E517" s="5" t="s">
-        <v>2355</v>
+        <v>2356</v>
       </c>
       <c r="F517" s="5" t="s">
-        <v>2384</v>
+        <v>2385</v>
       </c>
       <c r="G517" s="7"/>
       <c r="H517" s="5" t="s">
-        <v>2385</v>
+        <v>2386</v>
       </c>
       <c r="I517" s="7"/>
       <c r="J517" s="5" t="s">
         <v>1669</v>
       </c>
       <c r="K517" s="8" t="s">
-        <v>2220</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="518" spans="1:11" x14ac:dyDescent="0.2">
@@ -26315,20 +26381,20 @@
         <v>1637</v>
       </c>
       <c r="F518" s="5" t="s">
-        <v>2386</v>
+        <v>2387</v>
       </c>
       <c r="G518" s="7"/>
       <c r="H518" s="5" t="s">
-        <v>2387</v>
+        <v>2388</v>
       </c>
       <c r="I518" s="5" t="s">
-        <v>2388</v>
+        <v>2389</v>
       </c>
       <c r="J518" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K518" s="8" t="s">
-        <v>2389</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="519" spans="1:11" x14ac:dyDescent="0.2">
@@ -26342,26 +26408,26 @@
         <v>1472</v>
       </c>
       <c r="D519" s="5" t="s">
-        <v>2390</v>
+        <v>2391</v>
       </c>
       <c r="E519" s="5" t="s">
-        <v>2391</v>
+        <v>2392</v>
       </c>
       <c r="F519" s="5" t="s">
-        <v>2392</v>
+        <v>2393</v>
       </c>
       <c r="G519" s="7"/>
       <c r="H519" s="5" t="s">
-        <v>2393</v>
+        <v>2394</v>
       </c>
       <c r="I519" s="5" t="s">
-        <v>2394</v>
+        <v>2395</v>
       </c>
       <c r="J519" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K519" s="8" t="s">
-        <v>2395</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="520" spans="1:11" x14ac:dyDescent="0.2">
@@ -26375,26 +26441,26 @@
         <v>1472</v>
       </c>
       <c r="D520" s="5" t="s">
-        <v>2396</v>
+        <v>2397</v>
       </c>
       <c r="E520" s="5" t="s">
-        <v>2397</v>
+        <v>2398</v>
       </c>
       <c r="F520" s="5" t="s">
-        <v>2398</v>
+        <v>2399</v>
       </c>
       <c r="G520" s="7"/>
       <c r="H520" s="5" t="s">
-        <v>2399</v>
+        <v>2400</v>
       </c>
       <c r="I520" s="5" t="s">
-        <v>2400</v>
+        <v>2401</v>
       </c>
       <c r="J520" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K520" s="8" t="s">
-        <v>2401</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="521" spans="1:11" x14ac:dyDescent="0.2">
@@ -26408,62 +26474,68 @@
         <v>1472</v>
       </c>
       <c r="D521" s="5" t="s">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="E521" s="5" t="s">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="F521" s="5" t="s">
-        <v>2402</v>
+        <v>2403</v>
       </c>
       <c r="G521" s="7"/>
       <c r="H521" s="5" t="s">
-        <v>2403</v>
+        <v>2404</v>
       </c>
       <c r="I521" s="5" t="s">
-        <v>2404</v>
+        <v>2405</v>
       </c>
       <c r="J521" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K521" s="8" t="s">
-        <v>2405</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="522" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A522" s="4">
         <v>522</v>
       </c>
-      <c r="B522" s="7"/>
+      <c r="B522" s="5" t="s">
+        <v>11</v>
+      </c>
       <c r="C522" s="5" t="s">
         <v>1472</v>
       </c>
       <c r="D522" s="5" t="s">
-        <v>2172</v>
+        <v>2173</v>
       </c>
       <c r="E522" s="5" t="s">
-        <v>2173</v>
+        <v>2174</v>
       </c>
       <c r="F522" s="5" t="s">
-        <v>2406</v>
+        <v>2407</v>
       </c>
       <c r="G522" s="7"/>
       <c r="H522" s="5" t="s">
-        <v>2407</v>
-      </c>
-      <c r="I522" s="7"/>
+        <v>2408</v>
+      </c>
+      <c r="I522" s="5" t="s">
+        <v>2409</v>
+      </c>
       <c r="J522" s="5" t="s">
         <v>1669</v>
       </c>
       <c r="K522" s="8" t="s">
-        <v>2408</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="523" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A523" s="4">
         <v>523</v>
       </c>
-      <c r="B523" s="7"/>
+      <c r="B523" s="5" t="s">
+        <v>11</v>
+      </c>
       <c r="C523" s="5" t="s">
         <v>1472</v>
       </c>
@@ -26474,18 +26546,20 @@
         <v>1637</v>
       </c>
       <c r="F523" s="5" t="s">
-        <v>2409</v>
+        <v>2411</v>
       </c>
       <c r="G523" s="7"/>
       <c r="H523" s="5" t="s">
-        <v>2410</v>
-      </c>
-      <c r="I523" s="7"/>
+        <v>2412</v>
+      </c>
+      <c r="I523" s="5" t="s">
+        <v>2413</v>
+      </c>
       <c r="J523" s="5" t="s">
         <v>1669</v>
       </c>
       <c r="K523" s="8" t="s">
-        <v>2411</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="524" spans="1:11" x14ac:dyDescent="0.2">
@@ -26499,26 +26573,26 @@
         <v>1472</v>
       </c>
       <c r="D524" s="5" t="s">
-        <v>2396</v>
+        <v>2397</v>
       </c>
       <c r="E524" s="5" t="s">
-        <v>2397</v>
+        <v>2398</v>
       </c>
       <c r="F524" s="5" t="s">
-        <v>2412</v>
+        <v>2415</v>
       </c>
       <c r="G524" s="7"/>
       <c r="H524" s="5" t="s">
-        <v>2413</v>
+        <v>2416</v>
       </c>
       <c r="I524" s="5" t="s">
-        <v>2400</v>
+        <v>2401</v>
       </c>
       <c r="J524" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K524" s="8" t="s">
-        <v>2414</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="525" spans="1:11" x14ac:dyDescent="0.2">
@@ -26538,20 +26612,20 @@
         <v>1554</v>
       </c>
       <c r="F525" s="5" t="s">
-        <v>2415</v>
+        <v>2418</v>
       </c>
       <c r="G525" s="7"/>
       <c r="H525" s="5" t="s">
-        <v>2416</v>
+        <v>2419</v>
       </c>
       <c r="I525" s="5" t="s">
-        <v>2417</v>
+        <v>2420</v>
       </c>
       <c r="J525" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K525" s="8" t="s">
-        <v>2418</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="526" spans="1:11" x14ac:dyDescent="0.2">
@@ -26565,26 +26639,26 @@
         <v>1472</v>
       </c>
       <c r="D526" s="5" t="s">
-        <v>2419</v>
+        <v>2422</v>
       </c>
       <c r="E526" s="5" t="s">
-        <v>2420</v>
+        <v>2423</v>
       </c>
       <c r="F526" s="5" t="s">
-        <v>2421</v>
+        <v>2424</v>
       </c>
       <c r="G526" s="7"/>
       <c r="H526" s="5" t="s">
-        <v>2422</v>
+        <v>2425</v>
       </c>
       <c r="I526" s="5" t="s">
-        <v>2423</v>
+        <v>2426</v>
       </c>
       <c r="J526" s="5" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="K526" s="8" t="s">
-        <v>2424</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="527" spans="1:11" x14ac:dyDescent="0.2">
@@ -26598,24 +26672,24 @@
         <v>588</v>
       </c>
       <c r="D527" s="5" t="s">
-        <v>2425</v>
+        <v>2428</v>
       </c>
       <c r="E527" s="5" t="s">
-        <v>2426</v>
+        <v>2429</v>
       </c>
       <c r="F527" s="5" t="s">
-        <v>2427</v>
+        <v>2430</v>
       </c>
       <c r="G527" s="7"/>
       <c r="H527" s="5" t="s">
-        <v>2428</v>
+        <v>2431</v>
       </c>
       <c r="I527" s="7"/>
       <c r="J527" s="5" t="s">
         <v>619</v>
       </c>
       <c r="K527" s="8" t="s">
-        <v>2429</v>
+        <v>2432</v>
       </c>
     </row>
     <row r="528" spans="1:11" x14ac:dyDescent="0.2">
@@ -26635,20 +26709,20 @@
         <v>1637</v>
       </c>
       <c r="F528" s="5" t="s">
-        <v>2430</v>
+        <v>2433</v>
       </c>
       <c r="G528" s="7"/>
       <c r="H528" s="5" t="s">
-        <v>2431</v>
+        <v>2434</v>
       </c>
       <c r="I528" s="5" t="s">
-        <v>2432</v>
+        <v>2435</v>
       </c>
       <c r="J528" s="5" t="s">
         <v>1669</v>
       </c>
       <c r="K528" s="8" t="s">
-        <v>2433</v>
+        <v>2436</v>
       </c>
     </row>
     <row r="529" spans="1:11" x14ac:dyDescent="0.2">
@@ -26660,26 +26734,26 @@
         <v>67</v>
       </c>
       <c r="D529" s="5" t="s">
-        <v>2434</v>
+        <v>2437</v>
       </c>
       <c r="E529" s="5" t="s">
-        <v>2435</v>
+        <v>2438</v>
       </c>
       <c r="F529" s="5" t="s">
-        <v>2436</v>
+        <v>2439</v>
       </c>
       <c r="G529" s="7"/>
       <c r="H529" s="5" t="s">
-        <v>2437</v>
+        <v>2440</v>
       </c>
       <c r="I529" s="5" t="s">
-        <v>2438</v>
+        <v>2441</v>
       </c>
       <c r="J529" s="5" t="s">
         <v>223</v>
       </c>
       <c r="K529" s="8" t="s">
-        <v>2408</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="530" spans="1:11" x14ac:dyDescent="0.2">
@@ -26693,20 +26767,20 @@
         <v>277</v>
       </c>
       <c r="D530" s="5" t="s">
-        <v>2439</v>
+        <v>2443</v>
       </c>
       <c r="E530" s="5" t="s">
-        <v>2440</v>
+        <v>2444</v>
       </c>
       <c r="F530" s="5" t="s">
-        <v>2441</v>
+        <v>2445</v>
       </c>
       <c r="G530" s="7"/>
       <c r="H530" s="5" t="s">
-        <v>2442</v>
+        <v>2446</v>
       </c>
       <c r="I530" s="5" t="s">
-        <v>2443</v>
+        <v>2447</v>
       </c>
       <c r="J530" s="5" t="s">
         <v>283</v>
@@ -26722,22 +26796,22 @@
         <v>1472</v>
       </c>
       <c r="D531" s="5" t="s">
-        <v>2118</v>
+        <v>2119</v>
       </c>
       <c r="E531" s="5" t="s">
-        <v>2119</v>
+        <v>2120</v>
       </c>
       <c r="F531" s="5" t="s">
-        <v>2444</v>
+        <v>2448</v>
       </c>
       <c r="G531" s="7"/>
       <c r="H531" s="5" t="s">
-        <v>2445</v>
+        <v>2449</v>
       </c>
       <c r="I531" s="7"/>
       <c r="J531" s="7"/>
       <c r="K531" s="8" t="s">
-        <v>2446</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="532" spans="1:11" x14ac:dyDescent="0.2">
@@ -26751,26 +26825,26 @@
         <v>12</v>
       </c>
       <c r="D532" s="5" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="E532" s="5" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="F532" s="5" t="s">
-        <v>2447</v>
+        <v>2451</v>
       </c>
       <c r="G532" s="7"/>
       <c r="H532" s="5" t="s">
-        <v>2448</v>
+        <v>2452</v>
       </c>
       <c r="I532" s="5" t="s">
-        <v>2449</v>
+        <v>2453</v>
       </c>
       <c r="J532" s="5" t="s">
-        <v>2450</v>
+        <v>2454</v>
       </c>
       <c r="K532" s="8" t="s">
-        <v>2451</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="533" spans="1:11" x14ac:dyDescent="0.2">
@@ -26790,20 +26864,20 @@
         <v>977</v>
       </c>
       <c r="F533" s="5" t="s">
-        <v>2452</v>
+        <v>2456</v>
       </c>
       <c r="G533" s="7"/>
       <c r="H533" s="5" t="s">
-        <v>2453</v>
+        <v>2457</v>
       </c>
       <c r="I533" s="5" t="s">
-        <v>2454</v>
+        <v>2458</v>
       </c>
       <c r="J533" s="5" t="s">
-        <v>2455</v>
+        <v>2459</v>
       </c>
       <c r="K533" s="8" t="s">
-        <v>2456</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="534" spans="1:11" x14ac:dyDescent="0.2">
@@ -26817,26 +26891,26 @@
         <v>1472</v>
       </c>
       <c r="D534" s="5" t="s">
-        <v>2457</v>
+        <v>2461</v>
       </c>
       <c r="E534" s="5" t="s">
-        <v>2458</v>
+        <v>2462</v>
       </c>
       <c r="F534" s="5" t="s">
-        <v>2459</v>
+        <v>2463</v>
       </c>
       <c r="G534" s="7"/>
       <c r="H534" s="5" t="s">
-        <v>2460</v>
+        <v>2464</v>
       </c>
       <c r="I534" s="5" t="s">
-        <v>2461</v>
+        <v>2465</v>
       </c>
       <c r="J534" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K534" s="8" t="s">
-        <v>2462</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="535" spans="1:11" x14ac:dyDescent="0.2">
@@ -26850,26 +26924,26 @@
         <v>12</v>
       </c>
       <c r="D535" s="5" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="E535" s="5" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="F535" s="5" t="s">
-        <v>2463</v>
+        <v>2467</v>
       </c>
       <c r="G535" s="7"/>
       <c r="H535" s="5" t="s">
-        <v>2464</v>
+        <v>2468</v>
       </c>
       <c r="I535" s="5" t="s">
-        <v>2465</v>
+        <v>2469</v>
       </c>
       <c r="J535" s="5" t="s">
-        <v>2367</v>
+        <v>2368</v>
       </c>
       <c r="K535" s="8" t="s">
-        <v>2466</v>
+        <v>2470</v>
       </c>
     </row>
     <row r="536" spans="1:11" x14ac:dyDescent="0.2">
@@ -26883,26 +26957,26 @@
         <v>1472</v>
       </c>
       <c r="D536" s="5" t="s">
-        <v>2354</v>
+        <v>2355</v>
       </c>
       <c r="E536" s="5" t="s">
-        <v>2355</v>
+        <v>2356</v>
       </c>
       <c r="F536" s="5" t="s">
-        <v>2467</v>
+        <v>2471</v>
       </c>
       <c r="G536" s="7"/>
       <c r="H536" s="5" t="s">
-        <v>2468</v>
+        <v>2472</v>
       </c>
       <c r="I536" s="5" t="s">
-        <v>2469</v>
+        <v>2473</v>
       </c>
       <c r="J536" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K536" s="8" t="s">
-        <v>2470</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="537" spans="1:11" x14ac:dyDescent="0.2">
@@ -26914,24 +26988,24 @@
         <v>1472</v>
       </c>
       <c r="D537" s="5" t="s">
-        <v>2471</v>
+        <v>2475</v>
       </c>
       <c r="E537" s="5" t="s">
-        <v>2472</v>
+        <v>2476</v>
       </c>
       <c r="F537" s="5" t="s">
-        <v>2473</v>
+        <v>2477</v>
       </c>
       <c r="G537" s="7"/>
       <c r="H537" s="5" t="s">
-        <v>2474</v>
+        <v>2478</v>
       </c>
       <c r="I537" s="7"/>
       <c r="J537" s="5" t="s">
-        <v>2475</v>
+        <v>2479</v>
       </c>
       <c r="K537" s="8" t="s">
-        <v>2476</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="538" spans="1:11" x14ac:dyDescent="0.2">
@@ -26945,26 +27019,26 @@
         <v>1472</v>
       </c>
       <c r="D538" s="5" t="s">
-        <v>2477</v>
+        <v>2481</v>
       </c>
       <c r="E538" s="5" t="s">
-        <v>2478</v>
+        <v>2482</v>
       </c>
       <c r="F538" s="5" t="s">
-        <v>2479</v>
+        <v>2483</v>
       </c>
       <c r="G538" s="7"/>
       <c r="H538" s="5" t="s">
-        <v>2480</v>
+        <v>2484</v>
       </c>
       <c r="I538" s="5" t="s">
-        <v>2481</v>
+        <v>2485</v>
       </c>
       <c r="J538" s="5" t="s">
-        <v>2475</v>
+        <v>2479</v>
       </c>
       <c r="K538" s="8" t="s">
-        <v>2482</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="539" spans="1:11" x14ac:dyDescent="0.2">
@@ -26984,18 +27058,18 @@
         <v>971</v>
       </c>
       <c r="F539" s="5" t="s">
-        <v>2483</v>
+        <v>2487</v>
       </c>
       <c r="G539" s="7"/>
       <c r="H539" s="5" t="s">
-        <v>2484</v>
+        <v>2488</v>
       </c>
       <c r="I539" s="7"/>
       <c r="J539" s="5" t="s">
-        <v>2455</v>
+        <v>2459</v>
       </c>
       <c r="K539" s="8" t="s">
-        <v>2485</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="540" spans="1:11" x14ac:dyDescent="0.2">
@@ -27015,14 +27089,14 @@
         <v>1637</v>
       </c>
       <c r="F540" s="5" t="s">
-        <v>2486</v>
+        <v>2490</v>
       </c>
       <c r="G540" s="7"/>
       <c r="H540" s="5" t="s">
-        <v>2487</v>
+        <v>2491</v>
       </c>
       <c r="I540" s="5" t="s">
-        <v>2488</v>
+        <v>2492</v>
       </c>
       <c r="J540" s="5" t="s">
         <v>1669</v>
@@ -27046,14 +27120,14 @@
         <v>1519</v>
       </c>
       <c r="F541" s="5" t="s">
-        <v>2489</v>
+        <v>2493</v>
       </c>
       <c r="G541" s="7"/>
       <c r="H541" s="5" t="s">
-        <v>2490</v>
+        <v>2494</v>
       </c>
       <c r="I541" s="5" t="s">
-        <v>2491</v>
+        <v>2495</v>
       </c>
       <c r="J541" s="5" t="s">
         <v>1524</v>
@@ -27071,26 +27145,26 @@
         <v>12</v>
       </c>
       <c r="D542" s="5" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="E542" s="5" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="F542" s="5" t="s">
-        <v>2492</v>
+        <v>2496</v>
       </c>
       <c r="G542" s="7"/>
       <c r="H542" s="5" t="s">
-        <v>2493</v>
+        <v>2497</v>
       </c>
       <c r="I542" s="5" t="s">
-        <v>2494</v>
+        <v>2498</v>
       </c>
       <c r="J542" s="5" t="s">
         <v>555</v>
       </c>
       <c r="K542" s="8" t="s">
-        <v>2495</v>
+        <v>2499</v>
       </c>
     </row>
     <row r="543" spans="1:11" x14ac:dyDescent="0.2">
@@ -27110,20 +27184,20 @@
         <v>1554</v>
       </c>
       <c r="F543" s="5" t="s">
-        <v>2496</v>
+        <v>2500</v>
       </c>
       <c r="G543" s="7"/>
       <c r="H543" s="5" t="s">
-        <v>2497</v>
+        <v>2501</v>
       </c>
       <c r="I543" s="5" t="s">
-        <v>2498</v>
+        <v>2502</v>
       </c>
       <c r="J543" s="5" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="K543" s="8" t="s">
-        <v>2499</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="544" spans="1:11" x14ac:dyDescent="0.2">
@@ -27137,26 +27211,26 @@
         <v>12</v>
       </c>
       <c r="D544" s="5" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="E544" s="5" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="F544" s="5" t="s">
-        <v>2500</v>
+        <v>2504</v>
       </c>
       <c r="G544" s="7"/>
       <c r="H544" s="5" t="s">
-        <v>2501</v>
+        <v>2505</v>
       </c>
       <c r="I544" s="5" t="s">
-        <v>2502</v>
+        <v>2506</v>
       </c>
       <c r="J544" s="5" t="s">
-        <v>2200</v>
+        <v>2201</v>
       </c>
       <c r="K544" s="8" t="s">
-        <v>2503</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="545" spans="1:11" x14ac:dyDescent="0.2">
@@ -27176,14 +27250,14 @@
         <v>69</v>
       </c>
       <c r="F545" s="5" t="s">
-        <v>2504</v>
+        <v>2508</v>
       </c>
       <c r="G545" s="7"/>
       <c r="H545" s="5" t="s">
-        <v>2505</v>
+        <v>2509</v>
       </c>
       <c r="I545" s="5" t="s">
-        <v>2506</v>
+        <v>2510</v>
       </c>
       <c r="J545" s="5" t="s">
         <v>104</v>
@@ -27207,20 +27281,20 @@
         <v>1576</v>
       </c>
       <c r="F546" s="5" t="s">
-        <v>2507</v>
+        <v>2511</v>
       </c>
       <c r="G546" s="7"/>
       <c r="H546" s="5" t="s">
-        <v>2508</v>
+        <v>2512</v>
       </c>
       <c r="I546" s="5" t="s">
-        <v>2509</v>
+        <v>2513</v>
       </c>
       <c r="J546" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K546" s="8" t="s">
-        <v>2510</v>
+        <v>2514</v>
       </c>
     </row>
     <row r="547" spans="1:11" x14ac:dyDescent="0.2">
@@ -27240,20 +27314,20 @@
         <v>1576</v>
       </c>
       <c r="F547" s="5" t="s">
-        <v>2511</v>
+        <v>2515</v>
       </c>
       <c r="G547" s="7"/>
       <c r="H547" s="5" t="s">
-        <v>2512</v>
+        <v>2516</v>
       </c>
       <c r="I547" s="5" t="s">
-        <v>2513</v>
+        <v>2517</v>
       </c>
       <c r="J547" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K547" s="8" t="s">
-        <v>2514</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="548" spans="1:11" x14ac:dyDescent="0.2">
@@ -27273,20 +27347,20 @@
         <v>1756</v>
       </c>
       <c r="F548" s="5" t="s">
-        <v>2515</v>
+        <v>2519</v>
       </c>
       <c r="G548" s="7"/>
       <c r="H548" s="5" t="s">
-        <v>2516</v>
+        <v>2520</v>
       </c>
       <c r="I548" s="5" t="s">
-        <v>2517</v>
+        <v>2521</v>
       </c>
       <c r="J548" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K548" s="8" t="s">
-        <v>2518</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="549" spans="1:11" x14ac:dyDescent="0.2">
@@ -27306,20 +27380,20 @@
         <v>1648</v>
       </c>
       <c r="F549" s="5" t="s">
-        <v>2519</v>
+        <v>2523</v>
       </c>
       <c r="G549" s="7"/>
       <c r="H549" s="5" t="s">
-        <v>2520</v>
+        <v>2524</v>
       </c>
       <c r="I549" s="5" t="s">
-        <v>2521</v>
+        <v>2525</v>
       </c>
       <c r="J549" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K549" s="8" t="s">
-        <v>2522</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="550" spans="1:11" x14ac:dyDescent="0.2">
@@ -27333,20 +27407,20 @@
         <v>12</v>
       </c>
       <c r="D550" s="5" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="E550" s="5" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="F550" s="5" t="s">
-        <v>2523</v>
+        <v>2527</v>
       </c>
       <c r="G550" s="7"/>
       <c r="H550" s="5" t="s">
-        <v>2524</v>
+        <v>2528</v>
       </c>
       <c r="I550" s="5" t="s">
-        <v>2525</v>
+        <v>2529</v>
       </c>
       <c r="J550" s="5" t="s">
         <v>555</v>
@@ -27370,20 +27444,20 @@
         <v>106</v>
       </c>
       <c r="F551" s="5" t="s">
-        <v>2526</v>
+        <v>2530</v>
       </c>
       <c r="G551" s="7"/>
       <c r="H551" s="5" t="s">
-        <v>2527</v>
+        <v>2531</v>
       </c>
       <c r="I551" s="5" t="s">
-        <v>2528</v>
+        <v>2532</v>
       </c>
       <c r="J551" s="5" t="s">
-        <v>2529</v>
+        <v>2533</v>
       </c>
       <c r="K551" s="8" t="s">
-        <v>2530</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="552" spans="1:11" x14ac:dyDescent="0.2">
@@ -27403,17 +27477,17 @@
         <v>82</v>
       </c>
       <c r="F552" s="5" t="s">
-        <v>2531</v>
+        <v>2535</v>
       </c>
       <c r="G552" s="7"/>
       <c r="H552" s="5" t="s">
-        <v>2532</v>
+        <v>2536</v>
       </c>
       <c r="I552" s="5" t="s">
+        <v>2537</v>
+      </c>
+      <c r="J552" s="5" t="s">
         <v>2533</v>
-      </c>
-      <c r="J552" s="5" t="s">
-        <v>2529</v>
       </c>
       <c r="K552" s="6"/>
     </row>
@@ -27434,20 +27508,20 @@
         <v>76</v>
       </c>
       <c r="F553" s="5" t="s">
-        <v>2534</v>
+        <v>2538</v>
       </c>
       <c r="G553" s="7"/>
       <c r="H553" s="5" t="s">
-        <v>2535</v>
+        <v>2539</v>
       </c>
       <c r="I553" s="5" t="s">
-        <v>2536</v>
+        <v>2540</v>
       </c>
       <c r="J553" s="5" t="s">
-        <v>2529</v>
+        <v>2533</v>
       </c>
       <c r="K553" s="8" t="s">
-        <v>2537</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="554" spans="1:11" x14ac:dyDescent="0.2">
@@ -27459,26 +27533,26 @@
         <v>1472</v>
       </c>
       <c r="D554" s="5" t="s">
-        <v>2363</v>
+        <v>2364</v>
       </c>
       <c r="E554" s="5" t="s">
-        <v>2364</v>
+        <v>2365</v>
       </c>
       <c r="F554" s="5" t="s">
-        <v>2538</v>
+        <v>2542</v>
       </c>
       <c r="G554" s="7"/>
       <c r="H554" s="5" t="s">
-        <v>2539</v>
+        <v>2543</v>
       </c>
       <c r="I554" s="5" t="s">
-        <v>2540</v>
+        <v>2544</v>
       </c>
       <c r="J554" s="5" t="s">
-        <v>2367</v>
+        <v>2368</v>
       </c>
       <c r="K554" s="8" t="s">
-        <v>2541</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="555" spans="1:11" x14ac:dyDescent="0.2">
@@ -27498,14 +27572,14 @@
         <v>164</v>
       </c>
       <c r="F555" s="5" t="s">
-        <v>2542</v>
+        <v>2546</v>
       </c>
       <c r="G555" s="7"/>
       <c r="H555" s="5" t="s">
-        <v>2543</v>
+        <v>2547</v>
       </c>
       <c r="I555" s="5" t="s">
-        <v>2544</v>
+        <v>2548</v>
       </c>
       <c r="J555" s="5" t="s">
         <v>104</v>
@@ -27523,26 +27597,26 @@
         <v>765</v>
       </c>
       <c r="D556" s="5" t="s">
-        <v>2545</v>
+        <v>2549</v>
       </c>
       <c r="E556" s="5" t="s">
-        <v>2546</v>
+        <v>2550</v>
       </c>
       <c r="F556" s="5" t="s">
-        <v>2547</v>
+        <v>2551</v>
       </c>
       <c r="G556" s="7"/>
       <c r="H556" s="5" t="s">
-        <v>2548</v>
+        <v>2552</v>
       </c>
       <c r="I556" s="5" t="s">
-        <v>2549</v>
+        <v>2553</v>
       </c>
       <c r="J556" s="5" t="s">
         <v>785</v>
       </c>
       <c r="K556" s="8" t="s">
-        <v>2550</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="557" spans="1:11" x14ac:dyDescent="0.2">
@@ -27556,26 +27630,26 @@
         <v>765</v>
       </c>
       <c r="D557" s="5" t="s">
-        <v>2551</v>
+        <v>2555</v>
       </c>
       <c r="E557" s="5" t="s">
-        <v>2552</v>
+        <v>2556</v>
       </c>
       <c r="F557" s="5" t="s">
-        <v>2553</v>
+        <v>2557</v>
       </c>
       <c r="G557" s="7"/>
       <c r="H557" s="5" t="s">
-        <v>2552</v>
+        <v>2556</v>
       </c>
       <c r="I557" s="5" t="s">
-        <v>2554</v>
+        <v>2558</v>
       </c>
       <c r="J557" s="5" t="s">
         <v>797</v>
       </c>
       <c r="K557" s="8" t="s">
-        <v>2555</v>
+        <v>2559</v>
       </c>
     </row>
     <row r="558" spans="1:11" x14ac:dyDescent="0.2">
@@ -27589,26 +27663,26 @@
         <v>588</v>
       </c>
       <c r="D558" s="5" t="s">
-        <v>2556</v>
+        <v>2560</v>
       </c>
       <c r="E558" s="5" t="s">
-        <v>2557</v>
+        <v>2561</v>
       </c>
       <c r="F558" s="5" t="s">
-        <v>2558</v>
+        <v>2562</v>
       </c>
       <c r="G558" s="7"/>
       <c r="H558" s="5" t="s">
-        <v>2559</v>
+        <v>2563</v>
       </c>
       <c r="I558" s="5" t="s">
-        <v>2560</v>
+        <v>2564</v>
       </c>
       <c r="J558" s="5" t="s">
         <v>641</v>
       </c>
       <c r="K558" s="8" t="s">
-        <v>2561</v>
+        <v>2565</v>
       </c>
     </row>
     <row r="559" spans="1:11" x14ac:dyDescent="0.2">
@@ -27622,23 +27696,23 @@
         <v>67</v>
       </c>
       <c r="D559" s="5" t="s">
-        <v>2562</v>
+        <v>2566</v>
       </c>
       <c r="E559" s="5" t="s">
-        <v>2563</v>
+        <v>2567</v>
       </c>
       <c r="F559" s="5" t="s">
-        <v>2564</v>
+        <v>2568</v>
       </c>
       <c r="G559" s="7"/>
       <c r="H559" s="5" t="s">
-        <v>2565</v>
+        <v>2569</v>
       </c>
       <c r="I559" s="5" t="s">
-        <v>2536</v>
+        <v>2540</v>
       </c>
       <c r="J559" s="5" t="s">
-        <v>2529</v>
+        <v>2533</v>
       </c>
       <c r="K559" s="6"/>
     </row>
@@ -27653,26 +27727,26 @@
         <v>588</v>
       </c>
       <c r="D560" s="5" t="s">
-        <v>2270</v>
+        <v>2271</v>
       </c>
       <c r="E560" s="5" t="s">
-        <v>2271</v>
+        <v>2272</v>
       </c>
       <c r="F560" s="5" t="s">
-        <v>2566</v>
+        <v>2570</v>
       </c>
       <c r="G560" s="7"/>
       <c r="H560" s="5" t="s">
-        <v>2567</v>
+        <v>2571</v>
       </c>
       <c r="I560" s="5" t="s">
-        <v>2568</v>
+        <v>2572</v>
       </c>
       <c r="J560" s="5" t="s">
         <v>619</v>
       </c>
       <c r="K560" s="8" t="s">
-        <v>2569</v>
+        <v>2573</v>
       </c>
     </row>
     <row r="561" spans="1:11" x14ac:dyDescent="0.2">
@@ -27692,14 +27766,14 @@
         <v>1576</v>
       </c>
       <c r="F561" s="5" t="s">
-        <v>2570</v>
+        <v>2574</v>
       </c>
       <c r="G561" s="7"/>
       <c r="H561" s="5" t="s">
-        <v>2571</v>
+        <v>2575</v>
       </c>
       <c r="I561" s="5" t="s">
-        <v>2572</v>
+        <v>2576</v>
       </c>
       <c r="J561" s="5" t="s">
         <v>1524</v>
@@ -27715,26 +27789,26 @@
         <v>1472</v>
       </c>
       <c r="D562" s="5" t="s">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="E562" s="5" t="s">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="F562" s="5" t="s">
-        <v>2573</v>
+        <v>2577</v>
       </c>
       <c r="G562" s="7"/>
       <c r="H562" s="5" t="s">
-        <v>2574</v>
+        <v>2578</v>
       </c>
       <c r="I562" s="5" t="s">
-        <v>2575</v>
+        <v>2579</v>
       </c>
       <c r="J562" s="5" t="s">
         <v>1479</v>
       </c>
       <c r="K562" s="8" t="s">
-        <v>2576</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="563" spans="1:11" x14ac:dyDescent="0.2">
@@ -27746,26 +27820,26 @@
         <v>1472</v>
       </c>
       <c r="D563" s="5" t="s">
-        <v>2577</v>
+        <v>2581</v>
       </c>
       <c r="E563" s="5" t="s">
-        <v>2578</v>
+        <v>2582</v>
       </c>
       <c r="F563" s="5" t="s">
-        <v>2579</v>
+        <v>2583</v>
       </c>
       <c r="G563" s="7"/>
       <c r="H563" s="5" t="s">
-        <v>2580</v>
+        <v>2584</v>
       </c>
       <c r="I563" s="5" t="s">
-        <v>2581</v>
+        <v>2585</v>
       </c>
       <c r="J563" s="5" t="s">
         <v>1479</v>
       </c>
       <c r="K563" s="8" t="s">
-        <v>2582</v>
+        <v>2586</v>
       </c>
     </row>
     <row r="564" spans="1:11" x14ac:dyDescent="0.2">
@@ -27785,20 +27859,20 @@
         <v>14</v>
       </c>
       <c r="F564" s="5" t="s">
-        <v>2583</v>
+        <v>2587</v>
       </c>
       <c r="G564" s="7"/>
       <c r="H564" s="5" t="s">
-        <v>2584</v>
+        <v>2588</v>
       </c>
       <c r="I564" s="5" t="s">
-        <v>2585</v>
+        <v>2589</v>
       </c>
       <c r="J564" s="5" t="s">
         <v>555</v>
       </c>
       <c r="K564" s="8" t="s">
-        <v>2586</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="565" spans="1:11" x14ac:dyDescent="0.2">
@@ -27812,26 +27886,26 @@
         <v>1472</v>
       </c>
       <c r="D565" s="5" t="s">
-        <v>2587</v>
+        <v>2591</v>
       </c>
       <c r="E565" s="5" t="s">
-        <v>2588</v>
+        <v>2592</v>
       </c>
       <c r="F565" s="5" t="s">
-        <v>2589</v>
+        <v>2593</v>
       </c>
       <c r="G565" s="7"/>
       <c r="H565" s="5" t="s">
-        <v>2590</v>
+        <v>2594</v>
       </c>
       <c r="I565" s="5" t="s">
-        <v>2591</v>
+        <v>2595</v>
       </c>
       <c r="J565" s="5" t="s">
         <v>1524</v>
       </c>
       <c r="K565" s="8" t="s">
-        <v>2592</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="566" spans="1:11" x14ac:dyDescent="0.2">
@@ -27849,20 +27923,20 @@
         <v>1576</v>
       </c>
       <c r="F566" s="5" t="s">
-        <v>2593</v>
+        <v>2597</v>
       </c>
       <c r="G566" s="7"/>
       <c r="H566" s="5" t="s">
-        <v>2594</v>
+        <v>2598</v>
       </c>
       <c r="I566" s="5" t="s">
-        <v>2595</v>
+        <v>2599</v>
       </c>
       <c r="J566" s="5" t="s">
         <v>1479</v>
       </c>
       <c r="K566" s="8" t="s">
-        <v>2596</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="567" spans="1:11" x14ac:dyDescent="0.2">
@@ -27882,17 +27956,17 @@
         <v>25</v>
       </c>
       <c r="F567" s="5" t="s">
-        <v>2597</v>
+        <v>2601</v>
       </c>
       <c r="G567" s="7"/>
       <c r="H567" s="5" t="s">
-        <v>2598</v>
+        <v>2602</v>
       </c>
       <c r="I567" s="5" t="s">
-        <v>2599</v>
+        <v>2603</v>
       </c>
       <c r="J567" s="5" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
       <c r="K567" s="6"/>
     </row>
@@ -27905,17 +27979,17 @@
         <v>588</v>
       </c>
       <c r="D568" s="5" t="s">
-        <v>2600</v>
+        <v>2604</v>
       </c>
       <c r="E568" s="5" t="s">
-        <v>2601</v>
+        <v>2605</v>
       </c>
       <c r="F568" s="5" t="s">
-        <v>2602</v>
+        <v>2606</v>
       </c>
       <c r="G568" s="7"/>
       <c r="H568" s="5" t="s">
-        <v>2603</v>
+        <v>2607</v>
       </c>
       <c r="I568" s="7"/>
       <c r="J568" s="5" t="s">
@@ -27932,17 +28006,17 @@
         <v>588</v>
       </c>
       <c r="D569" s="5" t="s">
-        <v>2556</v>
+        <v>2560</v>
       </c>
       <c r="E569" s="5" t="s">
-        <v>2557</v>
+        <v>2561</v>
       </c>
       <c r="F569" s="5" t="s">
-        <v>2604</v>
+        <v>2608</v>
       </c>
       <c r="G569" s="7"/>
       <c r="H569" s="5" t="s">
-        <v>2605</v>
+        <v>2609</v>
       </c>
       <c r="I569" s="7"/>
       <c r="J569" s="5" t="s">
@@ -27959,17 +28033,17 @@
         <v>588</v>
       </c>
       <c r="D570" s="5" t="s">
-        <v>2606</v>
+        <v>2610</v>
       </c>
       <c r="E570" s="5" t="s">
-        <v>2607</v>
+        <v>2611</v>
       </c>
       <c r="F570" s="5" t="s">
-        <v>2608</v>
+        <v>2612</v>
       </c>
       <c r="G570" s="7"/>
       <c r="H570" s="5" t="s">
-        <v>2609</v>
+        <v>2613</v>
       </c>
       <c r="I570" s="7"/>
       <c r="J570" s="5" t="s">
@@ -27988,23 +28062,23 @@
         <v>277</v>
       </c>
       <c r="D571" s="5" t="s">
-        <v>2610</v>
+        <v>2614</v>
       </c>
       <c r="E571" s="5" t="s">
-        <v>2611</v>
+        <v>2615</v>
       </c>
       <c r="F571" s="5" t="s">
-        <v>2612</v>
+        <v>2616</v>
       </c>
       <c r="G571" s="7"/>
       <c r="H571" s="5" t="s">
-        <v>2613</v>
+        <v>2617</v>
       </c>
       <c r="I571" s="5" t="s">
-        <v>2614</v>
+        <v>2618</v>
       </c>
       <c r="J571" s="5" t="s">
-        <v>2615</v>
+        <v>2619</v>
       </c>
       <c r="K571" s="6"/>
     </row>
@@ -28025,11 +28099,11 @@
         <v>1362</v>
       </c>
       <c r="F572" s="5" t="s">
-        <v>2616</v>
+        <v>2620</v>
       </c>
       <c r="G572" s="7"/>
       <c r="H572" s="5" t="s">
-        <v>2617</v>
+        <v>2621</v>
       </c>
       <c r="I572" s="7"/>
       <c r="J572" s="5" t="s">
@@ -28052,18 +28126,18 @@
         <v>1474</v>
       </c>
       <c r="F573" s="5" t="s">
-        <v>2618</v>
+        <v>2622</v>
       </c>
       <c r="G573" s="7"/>
       <c r="H573" s="5" t="s">
-        <v>2619</v>
+        <v>2623</v>
       </c>
       <c r="I573" s="7"/>
       <c r="J573" s="5" t="s">
         <v>1669</v>
       </c>
       <c r="K573" s="8" t="s">
-        <v>2620</v>
+        <v>2624</v>
       </c>
     </row>
     <row r="574" spans="1:11" x14ac:dyDescent="0.2">
@@ -28077,57 +28151,123 @@
         <v>1472</v>
       </c>
       <c r="D574" s="5" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="E574" s="5" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="F574" s="5" t="s">
-        <v>2621</v>
+        <v>2625</v>
       </c>
       <c r="G574" s="7"/>
       <c r="H574" s="5" t="s">
-        <v>2622</v>
+        <v>2626</v>
       </c>
       <c r="I574" s="5" t="s">
-        <v>2623</v>
+        <v>2627</v>
       </c>
       <c r="J574" s="5" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="K574" s="8" t="s">
-        <v>2624</v>
+        <v>2628</v>
       </c>
     </row>
     <row r="575" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A575" s="9">
+      <c r="A575" s="4">
         <v>575</v>
       </c>
-      <c r="B575" s="10"/>
-      <c r="C575" s="11" t="s">
+      <c r="B575" s="7"/>
+      <c r="C575" s="5" t="s">
         <v>1472</v>
       </c>
-      <c r="D575" s="11" t="s">
-        <v>2625</v>
-      </c>
-      <c r="E575" s="11" t="s">
-        <v>2626</v>
-      </c>
-      <c r="F575" s="11" t="s">
-        <v>2627</v>
-      </c>
-      <c r="G575" s="10"/>
-      <c r="H575" s="11" t="s">
-        <v>2628</v>
-      </c>
-      <c r="I575" s="10"/>
-      <c r="J575" s="10"/>
-      <c r="K575" s="12" t="s">
+      <c r="D575" s="5" t="s">
         <v>2629</v>
       </c>
+      <c r="E575" s="5" t="s">
+        <v>2630</v>
+      </c>
+      <c r="F575" s="5" t="s">
+        <v>2631</v>
+      </c>
+      <c r="G575" s="7"/>
+      <c r="H575" s="5" t="s">
+        <v>2632</v>
+      </c>
+      <c r="I575" s="7"/>
+      <c r="J575" s="7"/>
+      <c r="K575" s="8" t="s">
+        <v>2633</v>
+      </c>
+    </row>
+    <row r="576" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A576" s="4">
+        <v>576</v>
+      </c>
+      <c r="B576" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C576" s="5" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D576" s="5" t="s">
+        <v>1497</v>
+      </c>
+      <c r="E576" s="5" t="s">
+        <v>1498</v>
+      </c>
+      <c r="F576" s="5" t="s">
+        <v>2634</v>
+      </c>
+      <c r="G576" s="7"/>
+      <c r="H576" s="5" t="s">
+        <v>2635</v>
+      </c>
+      <c r="I576" s="5" t="s">
+        <v>2636</v>
+      </c>
+      <c r="J576" s="5" t="s">
+        <v>1669</v>
+      </c>
+      <c r="K576" s="8" t="s">
+        <v>2637</v>
+      </c>
+    </row>
+    <row r="577" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A577" s="9">
+        <v>577</v>
+      </c>
+      <c r="B577" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C577" s="10" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D577" s="10" t="s">
+        <v>1636</v>
+      </c>
+      <c r="E577" s="10" t="s">
+        <v>1637</v>
+      </c>
+      <c r="F577" s="10" t="s">
+        <v>2638</v>
+      </c>
+      <c r="G577" s="11"/>
+      <c r="H577" s="10" t="s">
+        <v>2639</v>
+      </c>
+      <c r="I577" s="10" t="s">
+        <v>2640</v>
+      </c>
+      <c r="J577" s="10" t="s">
+        <v>1669</v>
+      </c>
+      <c r="K577" s="12" t="s">
+        <v>2641</v>
+      </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="BrefJekzLBpD8g51cp3SYQE7/z2psfnYxT0glbKRzX8uVn9PwkRA0lvzv4qXfT55rm5W3OSmOfU2qPGku6Zfkg==" saltValue="x2hr42WoLqthR+X0z/fWDg==" spinCount="100000" sheet="1" objects="1" scenarios="1" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="L6831uqv0TlWCK32MIfFOT7EmPluAaqrPqsYAfSPc9Cq6YoR5RDthiOvGUNwuXrWtxfHKoMx9ER6hAamV9f9aQ==" saltValue="0WpLZRpo1OeZd+MQNc7mWQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/RM.xlsx
+++ b/RM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FG &amp; RMPM LIST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CEB3941-0B1D-40D5-8D6C-9BE20E1BC16B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20EF99C8-661C-4524-A345-E35152BA857D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8740,41 +8740,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="16">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -9040,13 +9005,6 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -9065,6 +9023,48 @@
     <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -9079,20 +9079,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CB691F95-0A1C-4692-8B8B-1D0A40B9B473}" name="Table1" displayName="Table1" ref="A1:K577" totalsRowShown="0" headerRowDxfId="0" dataDxfId="15" headerRowBorderDxfId="13" tableBorderDxfId="14" totalsRowBorderDxfId="12">
-  <autoFilter ref="A1:K577" xr:uid="{CB691F95-0A1C-4692-8B8B-1D0A40B9B473}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C22ED967-55AA-4A3F-AAAC-1614CC662D9B}" name="Table1" displayName="Table1" ref="A1:K577" totalsRowShown="0" headerRowDxfId="15" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12" totalsRowBorderDxfId="11">
+  <autoFilter ref="A1:K577" xr:uid="{C22ED967-55AA-4A3F-AAAC-1614CC662D9B}"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{933C9A43-83B4-4237-8C82-B92A49062887}" name="ID" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{F7E718B2-ABD8-4A7C-979E-D2AE8AE50F4A}" name="Status" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{346A97BB-8D1C-4B2F-B6CB-B46126ABAB59}" name="Material List::Material_Detail" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{C743BD7A-D8A3-4650-915C-F338688B3A33}" name="Product_Code" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{F895AC09-2AB0-448D-8B67-F0158E16A7B5}" name="RM PM Product List 2::Product_Detail" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{F0254111-B0B6-4399-994A-6C9A0FB03B47}" name="Item_Code" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{B0A13EF6-C57C-4EA3-B440-43FC1ACB43C7}" name="Old_Item_Code" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{0E3E2A44-6890-43A7-9102-8A3A6599DF77}" name="Item_Name" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{76E54F0B-4253-4F26-A255-232797CB8A61}" name="Item_Detail_by_Vendor" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{8A507C32-61FE-4198-BA49-7F9573311229}" name="Vendor List 2::Vendor_Name" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{9C0C3A41-8807-4B1B-BD4D-1A3EFD5301DE}" name="Remarks" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{9B5F8BE2-2AC0-4A3B-9C13-D6228D2FD7BA}" name="ID" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{20C409E3-11F0-4FBF-A455-E5AB69EAF4CC}" name="Status" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{7D894566-B159-458E-B2FE-18E9FBC157F1}" name="Material List::Material_Detail" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{B3D74A60-BBA1-499D-ABD2-8B01CEF0BF78}" name="Product_Code" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{1F68A6DB-F482-4150-88B5-8228634AD42D}" name="RM PM Product List 2::Product_Detail" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{E78CD462-BB82-483C-A62A-6DB96B60CD86}" name="Item_Code" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{BAC6AD38-91E3-477F-8DA2-7307BEBA788E}" name="Old_Item_Code" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{43A3F27F-D8DC-4821-8BE2-ACBF43085FF2}" name="Item_Name" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{92DE3739-59BC-403F-9995-D114883A74FD}" name="Item_Detail_by_Vendor" dataDxfId="2"/>
+    <tableColumn id="10" xr3:uid="{F1E944FC-FDF5-4058-BFDB-A416E036F36A}" name="Vendor List 2::Vendor_Name" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{0D776452-4DAC-424B-A377-9F6BB97207B2}" name="Remarks" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -28267,7 +28267,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="L6831uqv0TlWCK32MIfFOT7EmPluAaqrPqsYAfSPc9Cq6YoR5RDthiOvGUNwuXrWtxfHKoMx9ER6hAamV9f9aQ==" saltValue="0WpLZRpo1OeZd+MQNc7mWQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" autoFilter="0"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="BSjb0rAIOIpY6CgCypB38zuP5OYH5HKPnDNEyprFxqmFL44sn9P2hHa+THDACg52ubxg2I8GIc2A1AHH2Fi/gQ==" saltValue="Bz5ECcB2STHm7x88NnUyHw==" spinCount="100000" sheet="1" objects="1" scenarios="1" autoFilter="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
